--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,348 +656,360 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45198</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44743</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44652</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44470</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44379</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44288</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44106</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44015</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43924</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43644</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43553</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43371</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>645600</v>
+      </c>
+      <c r="E8" s="3">
         <v>631300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>662400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>627200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>660800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>631100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>645800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>631400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>651800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>607300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1249800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>612600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>616300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>547200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>765600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>547200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>720500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>659300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2083900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>659700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1438500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>679500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E9" s="3">
         <v>267000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>279000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>263000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>291000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>263000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>269100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>257600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>268800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>250000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>516900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>251300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>268300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>235500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>352200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>266000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>331100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>292300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>440700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>296600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>298600</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>338600</v>
+      </c>
+      <c r="E10" s="3">
         <v>364300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>383400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>364200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>369800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>368100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>376700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>373800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>383000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>357300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>732900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>361300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>348000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>311700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>413400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>281200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>389400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>367000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1643200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>363100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1436200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>380900</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,85 +1037,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E12" s="3">
         <v>22300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>51700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>43500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>34700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>35400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>36300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>139100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>43300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>36000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>42300</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1179,74 +1195,77 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>268700</v>
+      </c>
+      <c r="E14" s="3">
         <v>6800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>58800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>57400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>51900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>1950500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>1943600</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1256,8 +1275,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1333,8 +1355,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1359,162 +1384,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>848400</v>
+      </c>
+      <c r="E17" s="3">
         <v>548000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>583500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>555100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>572800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>556600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>580600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>539900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>605700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>525600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1071400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>517500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>542800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>485600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>857200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>572200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>642500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>580600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>735600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>614800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>115300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>598100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-202800</v>
+      </c>
+      <c r="E18" s="3">
         <v>83300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>78900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>72100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>88000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>74500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>65200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>91500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>81700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>178400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>95100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>73500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>61600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-91600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>78000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>78700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1348300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>44900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1323200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>81400</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,25 +1574,26 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-32100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>300</v>
       </c>
       <c r="I20" s="3">
         <v>300</v>
@@ -1569,203 +1602,209 @@
         <v>300</v>
       </c>
       <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-168200</v>
+      </c>
+      <c r="E21" s="3">
         <v>84000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>119500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>108800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>125900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>110500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>100600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>123100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>79300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>112000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>240900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>126700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>105200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>96400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>109300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>156200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>318700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>77300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>160300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E22" s="3">
         <v>15400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>31600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>3300</v>
       </c>
       <c r="S22" s="3">
         <v>3300</v>
       </c>
       <c r="T22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>99400</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>115300</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1773,162 +1812,171 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="E23" s="3">
         <v>35800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>55700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>75700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>63200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>85900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>69900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>147400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>77400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>50800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-109200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>74600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>78700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>231800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>45000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3">
         <v>82900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-40300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-37000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>18500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>115300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18800</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2004,162 +2052,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-217400</v>
+      </c>
+      <c r="E26" s="3">
         <v>21500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>51900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>43800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>73500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>49600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>44500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>70400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>80200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>140800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>61800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>91100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-72200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>56100</v>
-      </c>
-      <c r="T26" s="3">
-        <v>62100</v>
       </c>
       <c r="U26" s="3">
         <v>62100</v>
       </c>
       <c r="V26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="W26" s="3">
         <v>37900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>154600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>64100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-217400</v>
+      </c>
+      <c r="E27" s="3">
         <v>21500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>51900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>43800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>73500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>49600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>44500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>70400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>80200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>140800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>61800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>91100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-72200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>56100</v>
-      </c>
-      <c r="T27" s="3">
-        <v>62100</v>
       </c>
       <c r="U27" s="3">
         <v>62100</v>
       </c>
       <c r="V27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="W27" s="3">
         <v>37900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>154600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>64100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2235,8 +2292,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,40 +2313,40 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-2000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>2600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>4500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>43300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>12700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>21000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>9900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>17300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>12000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-38500</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2312,8 +2372,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2389,8 +2452,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2466,25 +2532,28 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>32100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-300</v>
       </c>
       <c r="I32" s="3">
         <v>-300</v>
@@ -2493,135 +2562,141 @@
         <v>-300</v>
       </c>
       <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1017100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-217400</v>
+      </c>
+      <c r="E33" s="3">
         <v>21500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>51900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>73500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>47600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>47100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>74900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>85800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>92900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>161800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>71700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>108400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-110700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>56100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>62100</v>
       </c>
       <c r="U33" s="3">
         <v>62100</v>
       </c>
       <c r="V33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="W33" s="3">
         <v>37900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>154600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>64100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2697,167 +2772,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-217400</v>
+      </c>
+      <c r="E35" s="3">
         <v>21500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>51900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>73500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>47600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>47100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>74900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>85800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>92900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>161800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>71700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>108400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-110700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>56100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>62100</v>
       </c>
       <c r="U35" s="3">
         <v>62100</v>
       </c>
       <c r="V35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="W35" s="3">
         <v>37900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>154600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>64100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45198</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44743</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44652</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44470</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44379</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44288</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44106</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44015</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43924</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43644</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43553</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43371</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2885,8 +2969,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2914,65 +2999,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>940000</v>
+      </c>
+      <c r="E41" s="3">
         <v>824200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>651700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>585200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>606900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>568500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>523100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1078300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1073600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>638800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>553900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>441200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>888900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>822400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>353600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>211200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>193200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2991,8 +3077,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3068,68 +3157,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>407500</v>
+      </c>
+      <c r="E43" s="3">
         <v>417100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>415200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>401800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>393500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>392200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>372800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>342600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>331900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>307400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>355000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>358100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>361000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>365400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>306400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>365900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>443600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>456400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3602200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,68 +3237,71 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>258800</v>
+      </c>
+      <c r="E44" s="3">
         <v>278800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>297000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>307200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>300800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>291300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>286000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>280400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>263800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>274300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>311500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>283200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>266900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>257500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>280800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>312300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>277900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>278400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1624300</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,68 +3317,71 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>137400</v>
+      </c>
+      <c r="E45" s="3">
         <v>120600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>125000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>120100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>123400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>114000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>206400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>207600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>166500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>545900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>81300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>80800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>73700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>92500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>108100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>82400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>69200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>50500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1328700</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3299,68 +3397,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1743700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1640700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1488900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1414300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1424600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1366000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1388300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1908900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1835800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1766400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1301700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1163300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1590500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1416200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1517700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1114200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1001900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>978500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6009000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3477,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3420,32 +3524,32 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>22300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>4938800</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3453,68 +3557,71 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E48" s="3">
         <v>430600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>429700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>430500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>425400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>409300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>394600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>391200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>392200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>416900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>457800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>451200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>468300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>473900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>483200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>482600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>490400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>484900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17317700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,68 +3637,71 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4246200</v>
+      </c>
+      <c r="E49" s="3">
         <v>4459600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4536900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4571900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4583300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4463400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4465700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4097300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4178400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4204600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4574800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4580400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4689900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4642900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4589100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4551100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4591600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4574300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>623900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3717,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3684,8 +3797,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3761,68 +3877,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E52" s="3">
         <v>152900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>151700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>158300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>153700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>173200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>212400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>174900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>167800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>174100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>147000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>127000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>72700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>70700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>74400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>80700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>626800</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3838,8 +3957,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3915,68 +4037,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6605100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6683800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6607200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6575000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6587000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6411900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6461000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6572300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6574200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6562000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6481300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6321900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6876000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6605700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6665200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6240900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6158300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6118400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>154600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3992,8 +4117,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4021,8 +4149,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4050,65 +4179,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E57" s="3">
         <v>168600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>176800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>186800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>228300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>190000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>182700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>180600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>185800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>171000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>209400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>204600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>235100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>161100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>130900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>194800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>208000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>181400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4127,65 +4257,68 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E58" s="3">
         <v>115100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>511500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>510800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>510000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>579300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>508600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>507800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>432400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>426700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>421500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>416400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>886800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>253500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>152000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4204,68 +4337,71 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E59" s="3">
         <v>463100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>462500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>452000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>498400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>489000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>564900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>567300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>590000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>671500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>532300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>515300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>562800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>514000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>445800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>410600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>497300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>427300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5070100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4281,68 +4417,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>780800</v>
+      </c>
+      <c r="E60" s="3">
         <v>746800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1150800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1149600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1236700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1258300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1256200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1255700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1208200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1269200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1163200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1136300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1684700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>678900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>830200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>608900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>709200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>760700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17300</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4358,68 +4497,71 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1398100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1381000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>875600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>873800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>870700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>851600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>864100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>876900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>883400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>887800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>893200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>892200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>907700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1755500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1722200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1546700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1321000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1304500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4435,68 +4577,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>252300</v>
+      </c>
+      <c r="E62" s="3">
         <v>262800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>269800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>272600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>272700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>344100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>324700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>408800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>424600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>457900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>556000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>546100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>562600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>611500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>616900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>599000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>585300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>539200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>329200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4657,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4589,8 +4737,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4666,8 +4817,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4743,65 +4897,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2431200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2390600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2296200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2296000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2380100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2454000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2445000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2541400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2516600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2615300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2612800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2575000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3155400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3048100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3171800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2757200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2618100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2607100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4820,8 +4977,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4849,8 +5009,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4926,8 +5087,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5003,8 +5167,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5080,8 +5247,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5157,65 +5327,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>631200</v>
+      </c>
+      <c r="E72" s="3">
         <v>848600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>827100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>775200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>731400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>657900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>610300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>563200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>466900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>381100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>288200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>198100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>126400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>75900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>93100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5234,8 +5407,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5311,8 +5487,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5388,8 +5567,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5465,65 +5647,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4173900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4293200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4311000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4279000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4206900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3957900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4016000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4030900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4057600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3946700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3868500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3746900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3720600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3557600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3493400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3483700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3540200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3511300</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,8 +5727,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5619,167 +5807,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45198</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44743</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44652</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44470</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44379</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44288</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44106</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44015</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43924</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43644</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43553</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43371</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-217400</v>
+      </c>
+      <c r="E81" s="3">
         <v>21500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>51900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>73500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>47600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>47100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>74900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>85800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>92900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>161800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>71700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>108400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-110700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>56100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>62100</v>
       </c>
       <c r="U81" s="3">
         <v>62100</v>
       </c>
       <c r="V81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="W81" s="3">
         <v>37900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>154600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>64100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5807,85 +6004,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E83" s="3">
         <v>32800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>36400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>35700</v>
       </c>
       <c r="H83" s="3">
         <v>35700</v>
       </c>
       <c r="I83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="J83" s="3">
         <v>35100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>61900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>33100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>64900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>32000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>77300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-12500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>77400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5961,8 +6162,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6038,8 +6242,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6115,8 +6322,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6192,8 +6402,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6269,85 +6482,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E89" s="3">
         <v>95500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>75100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>110300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>46700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>136000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>137300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>193400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>148100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-57600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-62300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>187000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>281300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-61800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-225200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>210500</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6375,76 +6594,77 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>8900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-55200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-225200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6452,8 +6672,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6529,8 +6752,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6606,85 +6832,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-69700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-591600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>288600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-54400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-51400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-62600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>15300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15300</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>58900</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6712,8 +6944,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6789,8 +7022,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6866,8 +7102,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6943,8 +7182,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7020,71 +7262,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E100" s="3">
         <v>114500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-68300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>73700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-463100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-469600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-244400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>733100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>258500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-148100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>24300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7097,70 +7342,73 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>13600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>10800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -7174,70 +7422,73 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E102" s="3">
         <v>172500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>38400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>45400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-555200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>434800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>84900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-335000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-447700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>188100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-121600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>611200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>142400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -7249,6 +7500,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,360 +656,373 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45198</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44743</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44652</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44470</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44379</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44288</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44106</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44015</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43924</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43735</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43644</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43553</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43371</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>623600</v>
+      </c>
+      <c r="E8" s="3">
         <v>645600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>631300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>662400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>627200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>660800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>631100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>645800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>631400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>651800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>607300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1249800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>612600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>616300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>547200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>765600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>547200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>720500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>659300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2083900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>659700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1438500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>679500</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>265600</v>
+      </c>
+      <c r="E9" s="3">
         <v>307000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>267000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>279000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>263000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>291000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>263000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>269100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>257600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>268800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>250000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>516900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>251300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>268300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>235500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>352200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>266000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>331100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>292300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>440700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>296600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>298600</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E10" s="3">
         <v>338600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>364300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>383400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>364200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>369800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>368100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>376700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>373800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>383000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>357300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>732900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>361300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>348000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>311700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>413400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>281200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>389400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>367000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1643200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>363100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1436200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>380900</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,88 +1051,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E12" s="3">
         <v>20200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>51700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>43500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>34700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>35400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>36300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>139100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>43300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>36000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>42300</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1198,77 +1215,80 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E14" s="3">
         <v>268700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>58800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>57400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>39100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>51900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>1950500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1943600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
@@ -1278,8 +1298,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1358,8 +1381,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1385,168 +1411,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>575500</v>
+      </c>
+      <c r="E17" s="3">
         <v>848400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>548000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>583500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>555100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>572800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>556600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>580600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>539900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>605700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>525600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1071400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>517500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>542800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>485600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>857200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>572200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>642500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>580600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>735600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>614800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>115300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>598100</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-202800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>83300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>78900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>72100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>88000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>74500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>91500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>81700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>178400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>73500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>61600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-91600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-25000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>78000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>78700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1348300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>44900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1323200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>81400</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,28 +1608,29 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-32100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>300</v>
@@ -1605,209 +1639,215 @@
         <v>300</v>
       </c>
       <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>200</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>200</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-168200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>84000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>119500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>108800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>125900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>110500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>100600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>123100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>79300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>112000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>240900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>126700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>105200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>96400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>109300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>156200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>318700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>77300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>160300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E22" s="3">
         <v>13900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>3300</v>
       </c>
       <c r="T22" s="3">
         <v>3300</v>
       </c>
       <c r="U22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>99400</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>115300</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1815,168 +1855,177 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-215000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>35800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>68600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>55700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>75700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>63200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>59100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>85900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>69900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>147400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>77400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>50800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-109200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>74600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>78700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>231800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>45000</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3">
         <v>82900</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-10300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-40300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-37000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-11000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>115300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18800</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2055,168 +2104,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-217400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>43800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>73500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>49600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>44500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>70400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>42500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>80200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>140800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>61800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>91100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>23600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-72200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>56100</v>
-      </c>
-      <c r="U26" s="3">
-        <v>62100</v>
       </c>
       <c r="V26" s="3">
         <v>62100</v>
       </c>
       <c r="W26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="X26" s="3">
         <v>37900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>154600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>64100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-217400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>43800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>73500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>49600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>44500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>70400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>80200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>140800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>61800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>91100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>23600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-72200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>56100</v>
-      </c>
-      <c r="U27" s="3">
-        <v>62100</v>
       </c>
       <c r="V27" s="3">
         <v>62100</v>
       </c>
       <c r="W27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="X27" s="3">
         <v>37900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>154600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>64100</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2295,13 +2353,16 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2316,40 +2377,40 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>2600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>4500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>43300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>12700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>21000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>9900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>17300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>12000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-38500</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2375,8 +2436,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2455,8 +2519,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2535,28 +2602,31 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>32100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>-300</v>
@@ -2565,138 +2635,144 @@
         <v>-300</v>
       </c>
       <c r="L32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-200</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1017100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-217400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>43800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>73500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>47600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>74900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>85800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>92900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>161800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>108400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-110700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>56100</v>
-      </c>
-      <c r="U33" s="3">
-        <v>62100</v>
       </c>
       <c r="V33" s="3">
         <v>62100</v>
       </c>
       <c r="W33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="X33" s="3">
         <v>37900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>154600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>64100</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2775,173 +2851,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-217400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>43800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>73500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>47600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>74900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>85800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>92900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>161800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>108400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-110700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>56100</v>
-      </c>
-      <c r="U35" s="3">
-        <v>62100</v>
       </c>
       <c r="V35" s="3">
         <v>62100</v>
       </c>
       <c r="W35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="X35" s="3">
         <v>37900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>154600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>64100</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45198</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44743</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44652</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44470</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44379</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44288</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44106</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44015</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43924</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43735</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43644</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43553</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43371</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2970,8 +3055,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3000,68 +3086,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>948500</v>
+      </c>
+      <c r="E41" s="3">
         <v>940000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>824200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>651700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>585200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>606900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>568500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>523100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1078300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1073600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>638800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>553900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>441200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>888900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>700800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>822400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>353600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>211200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>193200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3167,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3160,71 +3250,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>413000</v>
+      </c>
+      <c r="E43" s="3">
         <v>407500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>417100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>415200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>401800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>393500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>392200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>372800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>342600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>331900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>307400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>355000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>358100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>361000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>365400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>306400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>365900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>443600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>456400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3602200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,71 +3333,74 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>267400</v>
+      </c>
+      <c r="E44" s="3">
         <v>258800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>278800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>297000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>307200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>291300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>286000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>280400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>263800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>274300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>311500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>283200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>266900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>257500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>280800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>312300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>277900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>278400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1624300</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3320,71 +3416,74 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E45" s="3">
         <v>137400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>120600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>125000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>120100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>123400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>114000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>206400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>207600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>166500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>545900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>81300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>80800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>73700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>92500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>108100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>82400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>69200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>50500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1328700</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,71 +3499,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1771900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1743700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1640700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1488900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1414300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1424600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1366000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1388300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1908900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1835800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1766400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1301700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1163300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1590500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1416200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1517700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1114200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1001900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>978500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6009000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3582,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3527,32 +3632,32 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>22300</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>4938800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3560,71 +3665,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>431500</v>
+      </c>
+      <c r="E48" s="3">
         <v>434700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>430600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>429700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>430500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>425400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>409300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>394600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>391200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>392200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>416900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>457800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>451200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>468300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>473900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>483200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>482600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>490400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>484900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17317700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3640,71 +3748,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4178500</v>
+      </c>
+      <c r="E49" s="3">
         <v>4246200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4459600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4536900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4571900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4583300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4463400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4465700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4097300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4178400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4204600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4574800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4580400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4689900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4642900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4589100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4551100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4591600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4574300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>623900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3831,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3800,8 +3914,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3880,71 +3997,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>174400</v>
+      </c>
+      <c r="E52" s="3">
         <v>180500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>152900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>151700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>158300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>153700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>173200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>212400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>174900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>167800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>174100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>147000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>127300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>72700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>75200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>70700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>74400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>80700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>626800</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3960,8 +4080,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4040,71 +4163,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6556300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6605100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6683800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6607200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6575000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6587000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6411900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6461000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6572300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6574200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6562000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6481300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6321900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6876000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6605700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6665200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6240900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6158300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6118400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>154600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4120,8 +4246,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4150,8 +4279,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4180,68 +4310,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E57" s="3">
         <v>179500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>168600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>176800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>186800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>228300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>190000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>182700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>180600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>185800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>171000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>209400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>204600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>235100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>161100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>130900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>194800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>208000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>181400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4260,68 +4391,71 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>115500</v>
+      </c>
+      <c r="E58" s="3">
         <v>115300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>115100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>511500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>510800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>510000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>579300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>508600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>507800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>432400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>426700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>421500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>416400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>886800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>253500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>152000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,71 +4474,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>491100</v>
+      </c>
+      <c r="E59" s="3">
         <v>486000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>463100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>462500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>452000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>498400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>489000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>564900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>567300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>590000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>671500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>532300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>515300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>562800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>514000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>445800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>410600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>497300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>427300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5070100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4420,71 +4557,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>781300</v>
+      </c>
+      <c r="E60" s="3">
         <v>780800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>746800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1150800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1149600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1236700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1258300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1256200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1255700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1208200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1269200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1163200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1136300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1684700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>678900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>830200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>608900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>709200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>760700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,71 +4640,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1390500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1398100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1381000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>875600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>873800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>870700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>851600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>864100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>876900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>883400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>887800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>893200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>892200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>907700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1755500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1722200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1546700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1321000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1304500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4580,71 +4723,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>244200</v>
+      </c>
+      <c r="E62" s="3">
         <v>252300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>262800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>269800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>272600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>272700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>344100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>324700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>408800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>424600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>457900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>556000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>546100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>562600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>611500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>616900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>599000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>585300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>539200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>329200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4806,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4740,8 +4889,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4820,8 +4972,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4900,68 +5055,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2431200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2390600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2296200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2296000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2380100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2454000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2445000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2541400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2516600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2615300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2612800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2575000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3155400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3048100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3171800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2757200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2618100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2607100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5138,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5010,8 +5171,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5090,8 +5252,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5170,8 +5335,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5250,8 +5418,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5330,68 +5501,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>654800</v>
+      </c>
+      <c r="E72" s="3">
         <v>631200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>848600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>827100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>775200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>731400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>657900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>610300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>563200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>466900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>381100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>288200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>198100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>126400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>75900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>93100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5410,8 +5584,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5490,8 +5667,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5570,8 +5750,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5650,68 +5833,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4140300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4173900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4293200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4311000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4279000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4206900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3957900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4016000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4030900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4057600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3946700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3868500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3746900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3720600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3557600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3493400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3483700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3540200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3511300</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5730,8 +5916,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5810,173 +5999,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45198</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44743</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44652</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44470</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44379</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44288</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44106</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44015</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43924</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43735</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43644</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43553</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43371</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-217400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>43800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>73500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>47600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>74900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>85800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>92900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>161800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>108400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-110700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>56100</v>
-      </c>
-      <c r="U81" s="3">
-        <v>62100</v>
       </c>
       <c r="V81" s="3">
         <v>62100</v>
       </c>
       <c r="W81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="X81" s="3">
         <v>37900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>154600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>64100</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6005,88 +6203,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E83" s="3">
         <v>32900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>36400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>35700</v>
       </c>
       <c r="I83" s="3">
         <v>35700</v>
       </c>
       <c r="J83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="K83" s="3">
         <v>35100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>61900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>33100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>34600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>77300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>-12500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>21400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>77400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6165,8 +6367,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6245,8 +6450,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6325,8 +6533,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6405,8 +6616,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6485,88 +6699,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E89" s="3">
         <v>102000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>95500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>75100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>110300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>136000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>137300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>193400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>148100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-57600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-62300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>187000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>281300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-61800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-225200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>210500</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6595,79 +6815,80 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>8900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-55200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-225200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6675,8 +6896,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6755,8 +6979,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6835,88 +7062,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-69700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-591600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>288600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-54400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-51400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-62600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>15300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15300</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>58900</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6945,8 +7178,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7025,8 +7259,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7105,8 +7342,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7185,8 +7425,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7265,74 +7508,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>114500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-68300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>73700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-463100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-469600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-244400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>733100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>258500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-148100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>24300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7345,73 +7591,76 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E101" s="3">
         <v>23100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>13600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-15700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
@@ -7425,73 +7674,76 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E102" s="3">
         <v>115800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>172500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>66500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>38400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>45400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-555200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>434800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>84900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-335000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-447700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>188100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-121600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>611200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>142400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
@@ -7503,6 +7755,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,373 +656,386 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E7" s="2">
         <v>45380</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45198</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44743</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44652</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44470</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44379</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44288</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44106</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44015</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43924</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43644</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43553</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43371</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>633100</v>
+      </c>
+      <c r="E8" s="3">
         <v>623600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>645600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>631300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>662400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>627200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>660800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>631100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>645800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>631400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>651800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>607300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1249800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>612600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>616300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>547200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>765600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>547200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>720500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>659300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2083900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>659700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1438500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>679500</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E9" s="3">
         <v>265600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>307000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>267000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>279000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>263000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>291000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>263000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>269100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>257600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>268800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>250000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>516900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>251300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>268300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>235500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>352200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>266000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>331100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>292300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>440700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>296600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>298600</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>329900</v>
+      </c>
+      <c r="E10" s="3">
         <v>358000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>338600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>364300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>383400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>364200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>369800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>368100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>376700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>373800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>383000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>357300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>732900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>361300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>348000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>311700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>413400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>281200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>389400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>367000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1643200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>363100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1436200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>380900</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1052,91 +1065,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E12" s="3">
         <v>23300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>51700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>43500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>35400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>36300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>139100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>43300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>36000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>42300</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,80 +1235,83 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1159600</v>
+      </c>
+      <c r="E14" s="3">
         <v>6900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>268700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>13600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>58800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>57400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>51900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>1950500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1943600</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
@@ -1301,8 +1321,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1384,8 +1407,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1412,174 +1438,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1786400</v>
+      </c>
+      <c r="E17" s="3">
         <v>575500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>848400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>548000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>583500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>555100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>572800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>556600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>580600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>539900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>605700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>525600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1071400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>517500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>542800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>485600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>857200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>572200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>642500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>580600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>735600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>614800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>115300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>598100</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1153300</v>
+      </c>
+      <c r="E18" s="3">
         <v>48100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-202800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>83300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>78900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>72100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>88000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>74500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>65200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>91500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>81700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>178400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>73500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>61600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-91600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-25000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>78000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>78700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1348300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>44900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1323200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>81400</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,31 +1642,32 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-32100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>300</v>
       </c>
       <c r="K20" s="3">
         <v>300</v>
@@ -1642,215 +1676,221 @@
         <v>300</v>
       </c>
       <c r="M20" s="3">
+        <v>300</v>
+      </c>
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1120400</v>
+      </c>
+      <c r="E21" s="3">
         <v>80300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-168200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>84000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>119500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>108800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>125900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>110500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>100600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>123100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>79300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>112000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>240900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>126700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>105200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>96400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-26500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>109300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>156200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>318700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>77300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>160300</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E22" s="3">
         <v>12900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>31600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>3300</v>
       </c>
       <c r="U22" s="3">
         <v>3300</v>
       </c>
       <c r="V22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>99400</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>115300</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -1858,174 +1898,183 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1166100</v>
+      </c>
+      <c r="E23" s="3">
         <v>35300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-215000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>35800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>68600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>55700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>75700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>63200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>59100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>85900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>69900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>147400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>77400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>50800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-109200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>74600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>78700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>231800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>45000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3">
         <v>82900</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E24" s="3">
         <v>11700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-10300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-40300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-37000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>115300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18800</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,174 +2156,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1151600</v>
+      </c>
+      <c r="E26" s="3">
         <v>23600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-217400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>51900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>43800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>73500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>49600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>44500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>70400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>80200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>140800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>61800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>91100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-72200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>56100</v>
-      </c>
-      <c r="V26" s="3">
-        <v>62100</v>
       </c>
       <c r="W26" s="3">
         <v>62100</v>
       </c>
       <c r="X26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Y26" s="3">
         <v>37900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>154600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>64100</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1151600</v>
+      </c>
+      <c r="E27" s="3">
         <v>23600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-217400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>43800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>73500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>49600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>44500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>70400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>80200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>140800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>61800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>91100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-72200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>56100</v>
-      </c>
-      <c r="V27" s="3">
-        <v>62100</v>
       </c>
       <c r="W27" s="3">
         <v>62100</v>
       </c>
       <c r="X27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Y27" s="3">
         <v>37900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>154600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>64100</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,16 +2414,19 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2380,40 +2441,40 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-2000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>2600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>4500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>43300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>12700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>21000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>9900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>17300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>12000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-38500</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2439,8 +2500,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,8 +2586,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,31 +2672,34 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>32100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-300</v>
       </c>
       <c r="K32" s="3">
         <v>-300</v>
@@ -2638,141 +2708,147 @@
         <v>-300</v>
       </c>
       <c r="M32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1017100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1151600</v>
+      </c>
+      <c r="E33" s="3">
         <v>23600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-217400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>43800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>73500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>74900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>85800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>92900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>161800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>71700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>108400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-110700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>56100</v>
-      </c>
-      <c r="V33" s="3">
-        <v>62100</v>
       </c>
       <c r="W33" s="3">
         <v>62100</v>
       </c>
       <c r="X33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Y33" s="3">
         <v>37900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>154600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>64100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,179 +2930,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1151600</v>
+      </c>
+      <c r="E35" s="3">
         <v>23600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-217400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>43800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>73500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>74900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>85800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>92900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>161800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>71700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>108400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-110700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>56100</v>
-      </c>
-      <c r="V35" s="3">
-        <v>62100</v>
       </c>
       <c r="W35" s="3">
         <v>62100</v>
       </c>
       <c r="X35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Y35" s="3">
         <v>37900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>154600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>64100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E38" s="2">
         <v>45380</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45198</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44743</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44652</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44470</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44379</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44288</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44106</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44015</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43924</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43644</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43553</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43371</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3056,8 +3141,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3087,71 +3173,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1036200</v>
+      </c>
+      <c r="E41" s="3">
         <v>948500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>940000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>824200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>651700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>585200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>606900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>568500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>523100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1078300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1073600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>638800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>553900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>441200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>888900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>700800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>822400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>353600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>211200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>193200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3257,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3253,74 +3343,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>380600</v>
+      </c>
+      <c r="E43" s="3">
         <v>413000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>407500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>417100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>415200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>401800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>393500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>392200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>372800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>342600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>331900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>307400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>355000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>358100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>361000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>365400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>306400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>365900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>443600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>456400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3602200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3336,74 +3429,77 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>263800</v>
+      </c>
+      <c r="E44" s="3">
         <v>267400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>258800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>278800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>297000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>307200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>291300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>286000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>280400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>263800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>274300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>311500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>283200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>266900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>257500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>280800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>312300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>277900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>278400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1624300</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3419,74 +3515,77 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E45" s="3">
         <v>143000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>137400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>120600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>125000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>120100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>123400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>114000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>206400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>207600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>166500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>545900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>81300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>80800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>73700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>92500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>108100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>82400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>69200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>50500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1328700</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3502,74 +3601,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1821900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1771900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1743700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1640700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1488900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1414300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1424600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1366000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1388300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1908900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1835800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1766400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1301700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1163300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1590500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1416200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1517700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1114200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1001900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>978500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6009000</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,8 +3687,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3635,32 +3740,32 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>22300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3">
         <v>4938800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3668,74 +3773,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>415800</v>
+      </c>
+      <c r="E48" s="3">
         <v>431500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>434700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>430600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>429700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>430500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>425400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>409300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>394600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>391200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>392200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>416900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>457800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>451200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>468300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>473900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>483200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>482600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>490400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>484900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>17317700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3751,74 +3859,77 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2981800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4178500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4246200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4459600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4536900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4571900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4583300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4463400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4465700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4097300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4178400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4204600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4574800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4580400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4689900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4642900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4589100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4551100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4591600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4574300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>623900</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3834,8 +3945,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,8 +4031,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,74 +4117,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E52" s="3">
         <v>174400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>180500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>152900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>151700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>158300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>153700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>173200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>212400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>174900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>167800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>174100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>147000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>127000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>127300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>72700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>75200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>70700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>74400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>80700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>626800</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4083,8 +4203,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,74 +4289,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5438100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6556300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6605100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6683800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6607200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6575000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6587000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6411900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6461000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6572300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6574200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6562000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6481300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6321900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6876000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6605700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6665200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6240900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6158300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6118400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>154600</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4249,8 +4375,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4280,8 +4409,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4311,71 +4441,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>172400</v>
+      </c>
+      <c r="E57" s="3">
         <v>174700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>179500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>168600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>176800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>186800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>228300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>190000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>182700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>180600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>185800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>171000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>209400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>204600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>235100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>161100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>130900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>194800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>208000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>181400</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,71 +4525,74 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E58" s="3">
         <v>115500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>115300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>115100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>511500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>510800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>510000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>579300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>508600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>507800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>432400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>426700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>421500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>416400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>886800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>253500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>152000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4477,74 +4611,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>533300</v>
+      </c>
+      <c r="E59" s="3">
         <v>491100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>486000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>463100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>462500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>452000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>498400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>489000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>564900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>567300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>590000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>671500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>532300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>515300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>562800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>514000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>445800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>410600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>497300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>427300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5070100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4560,74 +4697,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>821400</v>
+      </c>
+      <c r="E60" s="3">
         <v>781300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>780800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>746800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1150800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1149600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1236700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1258300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1256200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1255700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1208200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1269200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1163200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1136300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1684700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>678900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>830200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>608900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>709200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>760700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4643,74 +4783,77 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1388700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1390500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1398100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1381000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>875600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>873800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>870700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>851600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>864100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>876900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>883400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>887800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>893200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>892200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>907700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1755500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1722200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1546700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1321000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1304500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>25000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4726,74 +4869,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>251300</v>
+      </c>
+      <c r="E62" s="3">
         <v>244200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>252300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>262800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>269800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>272600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>272700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>344100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>324700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>408800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>424600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>457900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>556000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>546100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>562600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>611500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>616900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>599000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>585300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>539200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>329200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +4955,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,8 +5041,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,8 +5127,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,71 +5213,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2461400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2416000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2431200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2390600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2296200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2296000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2380100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2454000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2445000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2541400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2516600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2615300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2612800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2575000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3155400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3048100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3171800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2757200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2618100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2607100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5141,8 +5299,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5333,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,8 +5417,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,8 +5503,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,8 +5589,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,71 +5675,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-496800</v>
+      </c>
+      <c r="E72" s="3">
         <v>654800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>631200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>848600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>827100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>775200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>731400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>657900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>610300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>563200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>466900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>381100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>288200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>198100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>126400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>75900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>93100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5587,8 +5761,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,8 +5847,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,8 +5933,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,71 +6019,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2976700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4140300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4173900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4293200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4311000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4279000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4206900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3957900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4016000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4030900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4057600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3946700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3868500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3746900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3720600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3557600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3493400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3483700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3540200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3511300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5919,8 +6105,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,179 +6191,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E80" s="2">
         <v>45380</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45198</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44743</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44652</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44470</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44379</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44288</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44106</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44015</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43924</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43644</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43553</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43371</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1151600</v>
+      </c>
+      <c r="E81" s="3">
         <v>23600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-217400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>43800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>73500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>74900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>85800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>92900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>161800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>71700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>108400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-110700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>56100</v>
-      </c>
-      <c r="V81" s="3">
-        <v>62100</v>
       </c>
       <c r="W81" s="3">
         <v>62100</v>
       </c>
       <c r="X81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Y81" s="3">
         <v>37900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>154600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>64100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6204,91 +6402,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E83" s="3">
         <v>32100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>35700</v>
       </c>
       <c r="J83" s="3">
         <v>35700</v>
       </c>
       <c r="K83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="L83" s="3">
         <v>35100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>61900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>31300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>33100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>77300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>-12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>77400</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,8 +6572,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,8 +6658,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,8 +6744,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,8 +6830,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,91 +6916,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E89" s="3">
         <v>40300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>102000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>95500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>75100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>110300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>136000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>137300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>16600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>193400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>148100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-57600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-62300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>187000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>281300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-61800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-225200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>210500</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6816,82 +7036,83 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>8900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-55200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-225200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6899,8 +7120,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,8 +7206,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,91 +7292,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-69700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-591600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>288600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-54400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>15300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>58900</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7179,8 +7412,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7262,8 +7496,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,8 +7582,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,8 +7668,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,77 +7754,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>114500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-68300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>73700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-463100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-469600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-244400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>733100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>258500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-148100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3">
         <v>24300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7594,76 +7840,79 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>23100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>10800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-15700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5100</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
@@ -7677,76 +7926,79 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E102" s="3">
         <v>8500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>115800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>172500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>38400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>45400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-555200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>434800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>84900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-335000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-447700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>188100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-121600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>611200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>142400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
@@ -7758,6 +8010,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,386 +656,399 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E7" s="2">
         <v>45471</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45380</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45198</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44743</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44652</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44470</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44379</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44288</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44106</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44015</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43924</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43644</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43553</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43371</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>601000</v>
+      </c>
+      <c r="E8" s="3">
         <v>633100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>623600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>645600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>631300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>662400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>627200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>660800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>631100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>645800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>631400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>651800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>607300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1249800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>612600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>616300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>547200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>765600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>547200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>720500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>659300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2083900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>659700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>679500</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>283600</v>
+      </c>
+      <c r="E9" s="3">
         <v>303200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>265600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>307000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>267000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>279000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>263000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>291000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>263000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>269100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>257600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>268800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>250000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>516900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>251300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>268300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>235500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>352200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>266000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>331100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>292300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>440700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>296600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>298600</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>317400</v>
+      </c>
+      <c r="E10" s="3">
         <v>329900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>358000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>338600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>364300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>383400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>364200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>369800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>368100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>376700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>373800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>383000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>357300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>732900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>361300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>348000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>311700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>413400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>281200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>389400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>367000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1643200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>363100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>380900</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1066,94 +1079,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E12" s="3">
         <v>23600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22300</v>
       </c>
-      <c r="H12" s="3">
-        <v>18000</v>
-      </c>
       <c r="I12" s="3">
+        <v>26800</v>
+      </c>
+      <c r="J12" s="3">
         <v>24500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>51700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>34700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>35400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>36300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>139100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>43300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>36000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>42300</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1238,83 +1255,86 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1159600</v>
+        <v>1000</v>
       </c>
       <c r="E14" s="3">
+        <v>1161100</v>
+      </c>
+      <c r="F14" s="3">
         <v>6900</v>
       </c>
-      <c r="F14" s="3">
-        <v>268700</v>
-      </c>
       <c r="G14" s="3">
-        <v>6800</v>
+        <v>211200</v>
       </c>
       <c r="H14" s="3">
-        <v>13600</v>
+        <v>39100</v>
       </c>
       <c r="I14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J14" s="3">
         <v>4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>58800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>57400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>39100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>51900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1950500</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1324,31 +1344,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>29200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>32100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>32900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>32800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>36400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1410,8 +1433,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1439,180 +1465,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1786400</v>
+        <v>578500</v>
       </c>
       <c r="E17" s="3">
-        <v>575500</v>
+        <v>626800</v>
       </c>
       <c r="F17" s="3">
-        <v>848400</v>
+        <v>568600</v>
       </c>
       <c r="G17" s="3">
-        <v>548000</v>
+        <v>577200</v>
       </c>
       <c r="H17" s="3">
-        <v>583500</v>
+        <v>541200</v>
       </c>
       <c r="I17" s="3">
-        <v>555100</v>
+        <v>569900</v>
       </c>
       <c r="J17" s="3">
+        <v>550800</v>
+      </c>
+      <c r="K17" s="3">
         <v>572800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>556600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>580600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>539900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>605700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>525600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1071400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>517500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>542800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>485600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>857200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>572200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>642500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>580600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>735600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>614800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>115300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>598100</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1153300</v>
+        <v>22500</v>
       </c>
       <c r="E18" s="3">
-        <v>48100</v>
+        <v>6300</v>
       </c>
       <c r="F18" s="3">
-        <v>-202800</v>
+        <v>55000</v>
       </c>
       <c r="G18" s="3">
-        <v>83300</v>
+        <v>68400</v>
       </c>
       <c r="H18" s="3">
-        <v>78900</v>
+        <v>90100</v>
       </c>
       <c r="I18" s="3">
-        <v>72100</v>
+        <v>92500</v>
       </c>
       <c r="J18" s="3">
+        <v>76400</v>
+      </c>
+      <c r="K18" s="3">
         <v>88000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>74500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>65200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>91500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>81700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>178400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>95100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>73500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>61600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-91600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-25000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>78000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>78700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1348300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>44900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>81400</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1643,34 +1676,35 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1100</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>1700</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>-32100</v>
+        <v>58300</v>
       </c>
       <c r="H20" s="3">
-        <v>7100</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="J20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K20" s="3">
         <v>2200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>300</v>
       </c>
       <c r="L20" s="3">
         <v>300</v>
@@ -1679,221 +1713,227 @@
         <v>300</v>
       </c>
       <c r="N20" s="3">
+        <v>300</v>
+      </c>
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
+        <v>200</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1120400</v>
+        <v>51700</v>
       </c>
       <c r="E21" s="3">
-        <v>80300</v>
+        <v>40700</v>
       </c>
       <c r="F21" s="3">
-        <v>-168200</v>
+        <v>87200</v>
       </c>
       <c r="G21" s="3">
-        <v>84000</v>
+        <v>43000</v>
       </c>
       <c r="H21" s="3">
-        <v>119500</v>
+        <v>123100</v>
       </c>
       <c r="I21" s="3">
-        <v>108800</v>
+        <v>126200</v>
       </c>
       <c r="J21" s="3">
+        <v>113100</v>
+      </c>
+      <c r="K21" s="3">
         <v>125900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>110500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>100600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>123100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>79300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>112000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>240900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>126700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>105200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>96400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-26500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>109300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>156200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>318700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>77300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>160300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E22" s="3">
         <v>11700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>31600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17800</v>
-      </c>
-      <c r="U22" s="3">
-        <v>3300</v>
       </c>
       <c r="V22" s="3">
         <v>3300</v>
       </c>
       <c r="W22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>99400</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>115300</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -1901,180 +1941,189 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>35300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-215000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>35800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>68600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>55700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>75700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>63200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>85900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>69900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>147400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>77400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>50800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-109200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-28200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>74600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>78700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>231800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>45000</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3">
         <v>82900</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-40300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-37000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>115300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18800</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2159,180 +2208,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-217400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>51900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>43800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>73500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>44500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>70400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>42500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>80200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>140800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>61800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>91100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-72200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>56100</v>
-      </c>
-      <c r="W26" s="3">
-        <v>62100</v>
       </c>
       <c r="X26" s="3">
         <v>62100</v>
       </c>
       <c r="Y26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>37900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>154600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>64100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-217400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>43800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>73500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>49600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>44500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>70400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>80200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>140800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>61800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>91100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-72200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>56100</v>
-      </c>
-      <c r="W27" s="3">
-        <v>62100</v>
       </c>
       <c r="X27" s="3">
         <v>62100</v>
       </c>
       <c r="Y27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>37900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>154600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>64100</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2417,16 +2475,19 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2444,40 +2505,40 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-2000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>2600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>4500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>43300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>12700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>21000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>9900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>17300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>12000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-38500</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2503,8 +2564,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2589,8 +2653,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2675,34 +2742,37 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1100</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-1700</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>32100</v>
+        <v>-58300</v>
       </c>
       <c r="H32" s="3">
-        <v>-7100</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3">
+        <v>300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-300</v>
       </c>
       <c r="L32" s="3">
         <v>-300</v>
@@ -2711,144 +2781,150 @@
         <v>-300</v>
       </c>
       <c r="N32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1017100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-217400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>43800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>73500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>74900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>85800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>92900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>161800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>71700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>108400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-110700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>56100</v>
-      </c>
-      <c r="W33" s="3">
-        <v>62100</v>
       </c>
       <c r="X33" s="3">
         <v>62100</v>
       </c>
       <c r="Y33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>37900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>154600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>64100</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2933,185 +3009,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-217400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>43800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>73500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>74900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>85800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>92900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>161800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>71700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>108400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-110700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>56100</v>
-      </c>
-      <c r="W35" s="3">
-        <v>62100</v>
       </c>
       <c r="X35" s="3">
         <v>62100</v>
       </c>
       <c r="Y35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>37900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>154600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>64100</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E38" s="2">
         <v>45471</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45380</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45198</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44743</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44652</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44470</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44379</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44288</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44106</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44015</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43924</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43644</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43553</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43371</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3142,8 +3227,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3174,74 +3260,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>991300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1036200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>948500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>940000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>824200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>651700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>585200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>606900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>568500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>523100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1078300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1073600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>638800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>553900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>441200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>888900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>700800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>822400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>353600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>211200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>193200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3260,8 +3347,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3346,77 +3436,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>392100</v>
+      </c>
+      <c r="E43" s="3">
         <v>380600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>413000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>407500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>417100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>415200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>401800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>393500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>392200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>372800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>342600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>331900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>307400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>355000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>358100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>361000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>365400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>306400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>365900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>443600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>456400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3602200</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3432,77 +3525,80 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>265600</v>
+      </c>
+      <c r="E44" s="3">
         <v>263800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>267400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>258800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>278800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>297000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>307200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>291300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>286000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>280400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>263800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>274300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>311500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>283200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>266900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>257500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>280800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>312300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>277900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>278400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1624300</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3518,77 +3614,80 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>141300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
-        <v>143000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>137400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>120600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>125000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>120100</v>
-      </c>
-      <c r="J45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>123400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>114000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>206400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>207600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>166500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>545900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>81300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>80800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>73700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>92500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>108100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>82400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>69200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1328700</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3604,77 +3703,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1797000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1821900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1771900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1743700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1640700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1488900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1414300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1424600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1366000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1388300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1908900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1835800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1766400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1301700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1163300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1590500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1416200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1517700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1114200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1001900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>978500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6009000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3690,31 +3792,34 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3743,32 +3848,32 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>22300</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
         <v>4938800</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -3776,77 +3881,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>433200</v>
+      </c>
+      <c r="E48" s="3">
         <v>415800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>431500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>434700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>430600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>429700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>430500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>425400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>409300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>394600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>391200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>392200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>416900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>457800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>451200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>468300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>473900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>483200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>482600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>490400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>484900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17317700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,77 +3970,80 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3029900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2981800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4178500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4246200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4459600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4536900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4571900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4583300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4463400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4465700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4097300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4178400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4204600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4574800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4580400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4689900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4642900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4589100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4551100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4591600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4574300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>623900</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3948,8 +4059,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4034,8 +4148,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4120,77 +4237,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E52" s="3">
         <v>218600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>174400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>180500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>152900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>151700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>158300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>153700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>173200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>212400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>174900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>167800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>174100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>147000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>127000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>127300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>72700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>75200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>70700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>74400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>80700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>626800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4206,8 +4326,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4292,77 +4415,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5510700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5438100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6556300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6605100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6683800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6607200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6575000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6587000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6411900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6461000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6572300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6574200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6562000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6481300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6321900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6876000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6605700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6665200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6240900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6158300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6118400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>154600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4378,8 +4504,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4410,8 +4539,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4442,74 +4572,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E57" s="3">
         <v>172400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>174700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>179500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>168600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>176800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>186800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>228300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>190000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>182700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>180600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>185800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>171000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>209400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>204600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>235100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>161100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>130900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>194800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>208000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>181400</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,74 +4659,77 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>115700</v>
+        <v>152000</v>
       </c>
       <c r="E58" s="3">
-        <v>115500</v>
+        <v>150200</v>
       </c>
       <c r="F58" s="3">
-        <v>115300</v>
+        <v>148000</v>
       </c>
       <c r="G58" s="3">
-        <v>115100</v>
+        <v>145600</v>
       </c>
       <c r="H58" s="3">
-        <v>511500</v>
+        <v>144500</v>
       </c>
       <c r="I58" s="3">
-        <v>510800</v>
+        <v>540000</v>
       </c>
       <c r="J58" s="3">
+        <v>539200</v>
+      </c>
+      <c r="K58" s="3">
         <v>510000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>579300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>508600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>507800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>432400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>426700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>421500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>416400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>886800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>253500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>152000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4614,77 +4748,80 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>533300</v>
+        <v>314200</v>
       </c>
       <c r="E59" s="3">
-        <v>491100</v>
+        <v>301200</v>
       </c>
       <c r="F59" s="3">
-        <v>486000</v>
+        <v>286000</v>
       </c>
       <c r="G59" s="3">
-        <v>463100</v>
+        <v>257900</v>
       </c>
       <c r="H59" s="3">
-        <v>462500</v>
+        <v>236700</v>
       </c>
       <c r="I59" s="3">
-        <v>452000</v>
+        <v>250600</v>
       </c>
       <c r="J59" s="3">
+        <v>252700</v>
+      </c>
+      <c r="K59" s="3">
         <v>498400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>489000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>564900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>567300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>590000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>671500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>532300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>515300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>562800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>514000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>445800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>410600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>497300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>427300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5070100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4700,77 +4837,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>865500</v>
+      </c>
+      <c r="E60" s="3">
         <v>821400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>781300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>780800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>746800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1150800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1149600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1236700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1258300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1256200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1255700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1208200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1269200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1163200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1136300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1684700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>678900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>830200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>608900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>709200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>760700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4786,77 +4926,80 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1388700</v>
+        <v>1423000</v>
       </c>
       <c r="E61" s="3">
-        <v>1390500</v>
+        <v>1492500</v>
       </c>
       <c r="F61" s="3">
-        <v>1398100</v>
+        <v>1498000</v>
       </c>
       <c r="G61" s="3">
-        <v>1381000</v>
+        <v>1508000</v>
       </c>
       <c r="H61" s="3">
-        <v>875600</v>
+        <v>1493300</v>
       </c>
       <c r="I61" s="3">
-        <v>873800</v>
+        <v>992400</v>
       </c>
       <c r="J61" s="3">
+        <v>995100</v>
+      </c>
+      <c r="K61" s="3">
         <v>870700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>851600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>864100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>876900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>883400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>887800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>893200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>892200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>907700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1755500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1722200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1546700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1321000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1304500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>25000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4872,77 +5015,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>251300</v>
+        <v>103800</v>
       </c>
       <c r="E62" s="3">
-        <v>244200</v>
+        <v>104100</v>
       </c>
       <c r="F62" s="3">
-        <v>252300</v>
+        <v>103700</v>
       </c>
       <c r="G62" s="3">
-        <v>262800</v>
+        <v>103900</v>
       </c>
       <c r="H62" s="3">
-        <v>269800</v>
+        <v>127100</v>
       </c>
       <c r="I62" s="3">
-        <v>272600</v>
+        <v>128100</v>
       </c>
       <c r="J62" s="3">
+        <v>126800</v>
+      </c>
+      <c r="K62" s="3">
         <v>272700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>344100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>324700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>408800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>424600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>457900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>556000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>546100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>562600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>611500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>616900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>599000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>585300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>539200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>329200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4958,8 +5104,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5044,8 +5193,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5130,8 +5282,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5216,74 +5371,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2438200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2461400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2416000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2431200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2390600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2296200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2296000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2380100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2454000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2445000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2541400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2516600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2615300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2612800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2575000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3155400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3048100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3171800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2757200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2618100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2607100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5302,8 +5460,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5334,8 +5495,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5420,8 +5582,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5506,8 +5671,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5592,8 +5760,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5678,74 +5849,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-488600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-496800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>654800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>631200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>848600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>827100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>775200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>731400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>657900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>610300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>563200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>466900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>381100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>288200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>198100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>126400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-17600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>75900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>93100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5764,8 +5938,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5850,8 +6027,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5936,8 +6116,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6022,74 +6205,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3072500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2976700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4140300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4173900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4293200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4311000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4279000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4206900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3957900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4016000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4030900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4057600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3946700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3868500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3746900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3720600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3557600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3493400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3483700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3540200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3511300</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6108,8 +6294,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6194,185 +6383,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E80" s="2">
         <v>45471</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45380</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45198</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44743</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44652</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44470</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44379</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44288</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44106</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44015</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43924</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43644</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43553</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43371</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-217400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>43800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>73500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>74900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>85800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>92900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>161800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>71700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>108400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-110700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>56100</v>
-      </c>
-      <c r="W81" s="3">
-        <v>62100</v>
       </c>
       <c r="X81" s="3">
         <v>62100</v>
       </c>
       <c r="Y81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>37900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>154600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>64100</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6403,94 +6601,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>34000</v>
+        <v>8900</v>
       </c>
       <c r="E83" s="3">
-        <v>32100</v>
+        <v>2900</v>
       </c>
       <c r="F83" s="3">
-        <v>32900</v>
+        <v>15000</v>
       </c>
       <c r="G83" s="3">
-        <v>32800</v>
+        <v>14500</v>
       </c>
       <c r="H83" s="3">
-        <v>33500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>36400</v>
+        <v>14300</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
-        <v>35700</v>
+        <v>14200</v>
       </c>
       <c r="K83" s="3">
         <v>35700</v>
       </c>
       <c r="L83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="M83" s="3">
         <v>35100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>61900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>31300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>33100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>77300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>21400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>77400</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6575,8 +6777,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6661,8 +6866,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6747,8 +6955,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6833,8 +7044,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6919,94 +7133,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E89" s="3">
         <v>93100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>40300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>102000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>95500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>75100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>110300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>136000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>88300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>137300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>16600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>193400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>148100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-57600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-62300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>187000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>281300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-61800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>210500</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7037,85 +7257,86 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-21400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>8900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-55200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7123,8 +7344,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7209,8 +7433,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7295,94 +7522,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-69700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-591600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>288600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-54400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-51400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-62600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>15300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>58900</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7413,31 +7646,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7499,8 +7733,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7585,8 +7822,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7671,8 +7911,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7757,80 +8000,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100500</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>114500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-68300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>73700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-463100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-469600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-244400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>733100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>258500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-148100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3">
         <v>24300</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7843,79 +8089,82 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>200</v>
+        <v>-12500</v>
       </c>
       <c r="E101" s="3">
-        <v>-18500</v>
+        <v>-8400</v>
       </c>
       <c r="F101" s="3">
-        <v>23100</v>
+        <v>-1300</v>
       </c>
       <c r="G101" s="3">
-        <v>-12500</v>
+        <v>-2500</v>
       </c>
       <c r="H101" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-1300</v>
+        <v>-5300</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>8400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-15700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
@@ -7929,79 +8178,82 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-44900</v>
+      </c>
+      <c r="E102" s="3">
         <v>87700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>115800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>172500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>38400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>45400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-555200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>434800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>84900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-335000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-447700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>188100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-121600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>611200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>142400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
@@ -8013,6 +8265,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,399 +656,411 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45562</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45471</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45380</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45198</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44743</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44652</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44470</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44379</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44288</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44106</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44015</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43924</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43644</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43553</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43371</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>652900</v>
+      </c>
+      <c r="E8" s="3">
         <v>601000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>633100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>623600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>645600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>631300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>662400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>627200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>660800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>631100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>645800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>631400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>651800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>607300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1249800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>612600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>616300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>547200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>765600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>547200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>720500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>659300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2083900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>659700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>679500</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>279600</v>
+      </c>
+      <c r="E9" s="3">
         <v>283600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>303200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>265600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>307000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>267000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>279000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>263000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>291000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>263000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>269100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>257600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>268800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>250000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>516900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>251300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>268300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>235500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>352200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>266000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>331100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>292300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>440700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>296600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>298600</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>373300</v>
+      </c>
+      <c r="E10" s="3">
         <v>317400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>329900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>358000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>338600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>364300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>383400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>364200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>369800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>368100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>376700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>373800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>383000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>357300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>732900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>361300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>348000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>311700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>413400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>281200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>389400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>367000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1643200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>363100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>380900</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1080,97 +1092,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E12" s="3">
         <v>25500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>51700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>43500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>35400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>36300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>139100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>43300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>36000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>42300</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1258,86 +1274,89 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1161100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6900</v>
       </c>
-      <c r="G14" s="3">
-        <v>211200</v>
-      </c>
       <c r="H14" s="3">
+        <v>268700</v>
+      </c>
+      <c r="I14" s="3">
         <v>39100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>58800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>57400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>39100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>51900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1950500</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1347,35 +1366,38 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E15" s="3">
         <v>29200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>34000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>32100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>32800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>33500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1436,8 +1458,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1466,186 +1491,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>593300</v>
+      </c>
+      <c r="E17" s="3">
         <v>578500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>626800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>568600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>577200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>541200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>569900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>550800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>572800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>556600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>580600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>539900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>605700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>525600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1071400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>517500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>542800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>485600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>857200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>572200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>642500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>580600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>735600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>614800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>115300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>598100</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E18" s="3">
         <v>22500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>55000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>68400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>90100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>92500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>76400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>88000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>74500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>65200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>91500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>81700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>178400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>95100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>73500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>61600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-91600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-25000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>78000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>78700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1348300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>44900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>81400</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1677,37 +1709,38 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>58300</v>
-      </c>
       <c r="H20" s="3">
-        <v>-200</v>
+        <v>800</v>
       </c>
       <c r="I20" s="3">
         <v>-200</v>
       </c>
       <c r="J20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>300</v>
       </c>
       <c r="M20" s="3">
         <v>300</v>
@@ -1716,227 +1749,233 @@
         <v>300</v>
       </c>
       <c r="O20" s="3">
+        <v>300</v>
+      </c>
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>200</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E21" s="3">
         <v>51700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>87200</v>
       </c>
-      <c r="G21" s="3">
-        <v>43000</v>
-      </c>
       <c r="H21" s="3">
+        <v>100500</v>
+      </c>
+      <c r="I21" s="3">
         <v>123100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>126200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>113100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>125900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>110500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>100600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>123100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>79300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>112000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>240900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>126700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>105200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>96400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-26500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>109300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>156200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>318700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>77300</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>160300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>11900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>31600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17800</v>
-      </c>
-      <c r="V22" s="3">
-        <v>3300</v>
       </c>
       <c r="W22" s="3">
         <v>3300</v>
       </c>
       <c r="X22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>99400</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>115300</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
@@ -1944,186 +1983,195 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E23" s="3">
         <v>9600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>35300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-215000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>35800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>68600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>55700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>75700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>63200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>85900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>69900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>147400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>77400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>50800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>38400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-109200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-28200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>74600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>78700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>231800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>45000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="3">
         <v>82900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-40300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-37000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>15700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>115300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18800</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2211,186 +2259,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-217400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>51900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>73500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>44500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>70400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>42500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>80200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>140800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>61800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>91100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-72200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>56100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>62100</v>
       </c>
       <c r="Y26" s="3">
         <v>62100</v>
       </c>
       <c r="Z26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>37900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>154600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>64100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-217400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>51900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>43800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>73500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>49600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>44500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>70400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>80200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>140800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>61800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>91100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-72200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>56100</v>
-      </c>
-      <c r="X27" s="3">
-        <v>62100</v>
       </c>
       <c r="Y27" s="3">
         <v>62100</v>
       </c>
       <c r="Z27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>37900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>154600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>64100</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2478,8 +2535,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,40 +2568,40 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-2000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>2600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>4500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>43300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>12700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>21000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>9900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>17300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>12000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-38500</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2567,8 +2627,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2656,8 +2719,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2745,37 +2811,40 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-58300</v>
-      </c>
       <c r="H32" s="3">
-        <v>200</v>
+        <v>-800</v>
       </c>
       <c r="I32" s="3">
         <v>200</v>
       </c>
       <c r="J32" s="3">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-300</v>
       </c>
       <c r="M32" s="3">
         <v>-300</v>
@@ -2784,147 +2853,153 @@
         <v>-300</v>
       </c>
       <c r="O32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1017100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-217400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>51900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>43800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>73500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>47100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>74900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>85800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>92900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>161800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>71700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>108400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-110700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>56100</v>
-      </c>
-      <c r="X33" s="3">
-        <v>62100</v>
       </c>
       <c r="Y33" s="3">
         <v>62100</v>
       </c>
       <c r="Z33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>37900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>154600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>64100</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3012,191 +3087,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-217400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>51900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>43800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>73500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>47100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>74900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>85800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>92900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>161800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>71700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>108400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-110700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>56100</v>
-      </c>
-      <c r="X35" s="3">
-        <v>62100</v>
       </c>
       <c r="Y35" s="3">
         <v>62100</v>
       </c>
       <c r="Z35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>37900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>154600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>64100</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45562</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45471</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45380</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45198</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44743</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44652</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44470</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44379</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44288</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44106</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44015</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43924</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43644</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43553</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43371</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3228,8 +3312,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3261,77 +3346,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1069100</v>
+      </c>
+      <c r="E41" s="3">
         <v>991300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1036200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>948500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>940000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>824200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>651700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>585200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>606900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>568500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>523100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1078300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1073600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>638800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>553900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>441200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>888900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>700800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>822400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>353600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>211200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>193200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3436,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3439,80 +3528,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>363000</v>
+      </c>
+      <c r="E43" s="3">
         <v>392100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>380600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>413000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>407500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>417100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>415200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>401800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>393500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>392200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>372800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>342600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>331900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>307400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>355000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>358100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>361000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>365400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>306400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>365900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>443600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>456400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3602200</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3528,80 +3620,83 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E44" s="3">
         <v>265600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>263800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>267400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>258800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>278800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>297000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>307200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>300800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>291300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>286000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>280400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>263800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>274300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>311500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>283200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>266900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>257500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>280800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>312300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>277900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>278400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1624300</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3617,20 +3712,23 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,54 +3741,54 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>123400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>114000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>206400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>207600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>166500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>545900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>81300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>80800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>73700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>92500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>108100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>69200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>50500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1328700</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3706,80 +3804,83 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1788300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1797000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1821900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1771900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1743700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1640700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1488900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1414300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1424600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1366000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1388300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1908900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1835800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1766400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1301700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1163300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1590500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1416200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1517700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1114200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1001900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>978500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6009000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,8 +3896,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3821,8 +3925,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3851,32 +3955,32 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>22300</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3">
         <v>4938800</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -3884,80 +3988,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>419800</v>
+      </c>
+      <c r="E48" s="3">
         <v>433200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>415800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>431500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>434700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>430600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>429700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>430500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>425400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>409300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>394600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>391200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>392200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>416900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>457800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>451200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>468300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>473900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>483200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>482600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>490400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>484900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17317700</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3973,80 +4080,83 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2911800</v>
+      </c>
+      <c r="E49" s="3">
         <v>3029900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2981800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4178500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4246200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4459600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4536900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4571900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4583300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4463400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4465700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4097300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4178400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4204600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4574800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4580400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4689900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4642900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4589100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4551100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4591600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4574300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>623900</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4062,8 +4172,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4151,8 +4264,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4240,80 +4356,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E52" s="3">
         <v>250600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>218600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>174400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>180500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>152900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>151700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>158300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>153700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>173200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>212400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>174900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>167800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>174100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>147000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>127000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>127300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>72700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>75200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>70700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>74400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>80700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>626800</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4329,8 +4448,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4418,80 +4540,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5350500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5510700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5438100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6556300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6605100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6683800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6607200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6575000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6587000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6411900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6461000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6572300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6574200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6562000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6481300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6321900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6876000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6605700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6665200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6240900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6158300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6118400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>154600</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4507,8 +4632,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4540,8 +4668,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4573,77 +4702,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>174600</v>
+      </c>
+      <c r="E57" s="3">
         <v>172100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>172400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>174700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>179500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>168600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>176800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>186800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>228300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>190000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>182700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>180600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>185800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>171000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>209400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>204600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>235100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>161100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>130900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>194800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>208000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>181400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,77 +4792,80 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>150500</v>
+      </c>
+      <c r="E58" s="3">
         <v>152000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>150200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>148000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>145600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>144500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>540000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>539200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>510000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>579300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>508600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>507800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>432400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>426700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>421500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>416400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>886800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>253500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>152000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4751,80 +4884,83 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>317200</v>
+      </c>
+      <c r="E59" s="3">
         <v>314200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>301200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>286000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>257900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>236700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>250600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>252700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>498400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>489000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>564900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>567300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>590000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>671500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>532300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>515300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>562800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>514000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>445800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>410600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>497300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>427300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5070100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4840,80 +4976,83 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>878700</v>
+      </c>
+      <c r="E60" s="3">
         <v>865500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>821400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>781300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>780800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>746800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1150800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1149600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1236700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1258300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1256200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1255700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1208200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1269200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1163200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1136300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1684700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>678900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>830200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>608900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>709200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>760700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17300</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4929,80 +5068,83 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1397200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1423000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1492500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1498000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1508000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1493300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>992400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>995100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>870700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>851600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>864100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>876900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>883400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>887800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>893200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>892200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>907700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1755500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1722200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1546700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1321000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1304500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5018,80 +5160,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E62" s="3">
         <v>103800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>103700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>103900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>127100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>128100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>126800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>272700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>344100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>324700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>408800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>424600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>457900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>556000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>546100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>562600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>611500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>616900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>599000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>585300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>539200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>329200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5107,8 +5252,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5196,8 +5344,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5285,8 +5436,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5374,77 +5528,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2415700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2438200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2461400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2416000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2431200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2390600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2296200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2296000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2380100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2454000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2445000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2541400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2516600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2615300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2612800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2575000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3155400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3048100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3171800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2757200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2618100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2607100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5463,8 +5620,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5496,8 +5656,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5585,8 +5746,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5674,8 +5838,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5763,8 +5930,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5852,77 +6022,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-487400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-488600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-496800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>654800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>631200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>848600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>827100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>775200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>731400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>657900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>610300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>563200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>466900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>381100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>288200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>198100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>126400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>75900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>93100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>37000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5941,8 +6114,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6030,8 +6206,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6119,8 +6298,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6208,77 +6390,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2934800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3072500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2976700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4140300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4173900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4293200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4311000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4279000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4206900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3957900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4016000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4030900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4057600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3946700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3868500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3746900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3720600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3557600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3493400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3483700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3540200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3511300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6482,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6386,191 +6574,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45562</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45471</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45380</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45198</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44743</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44652</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44470</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44379</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44288</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44106</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44015</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43924</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43644</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43553</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43371</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-217400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>51900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>43800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>73500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>47100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>74900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>85800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>92900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>161800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>71700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>108400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-110700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>56100</v>
-      </c>
-      <c r="X81" s="3">
-        <v>62100</v>
       </c>
       <c r="Y81" s="3">
         <v>62100</v>
       </c>
       <c r="Z81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>37900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>154600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>64100</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6602,97 +6799,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E83" s="3">
         <v>8900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14300</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>14200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>35700</v>
       </c>
       <c r="L83" s="3">
         <v>35700</v>
       </c>
       <c r="M83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="N83" s="3">
         <v>35100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>31300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>33100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>34600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>64900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>77300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>21400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>77400</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6780,8 +6981,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6869,8 +7073,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6958,8 +7165,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7047,8 +7257,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7136,97 +7349,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>132400</v>
+      </c>
+      <c r="E89" s="3">
         <v>70700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>93100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>40300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>102000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>95500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>75100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>110300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>136000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>137300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>193400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>148100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-57600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-62300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>187000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>281300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-61800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>210500</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7258,88 +7477,89 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-21400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>8900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-55200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7347,8 +7567,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7436,8 +7659,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7525,97 +7751,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-69700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-591600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>288600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-54400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-51400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-62600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>15300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>58900</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7647,8 +7879,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7673,8 +7906,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7736,8 +7969,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7825,8 +8061,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7914,8 +8153,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8003,83 +8245,86 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>114500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-68300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>73700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-463100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-469600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-244400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>733100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>258500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-148100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3">
         <v>24300</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8092,82 +8337,85 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-9200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>10800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-15700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-5100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
@@ -8181,82 +8429,85 @@
       <c r="AE101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-44900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>115800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>172500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>45400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-555200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>434800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>84900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-335000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-447700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>188100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-121600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>611200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>142400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
@@ -8268,6 +8519,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,411 +656,424 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45562</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45471</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45380</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45198</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44743</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44652</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44470</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44379</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44288</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44106</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44015</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43924</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43644</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43553</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43371</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>616900</v>
+      </c>
+      <c r="E8" s="3">
         <v>652900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>601000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>633100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>623600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>645600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>631300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>662400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>627200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>660800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>631100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>645800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>631400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>651800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>607300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1249800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>612600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>616300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>547200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>765600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>547200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>720500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>659300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2083900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>659700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>679500</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E9" s="3">
         <v>279600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>283600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>303200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>265600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>307000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>267000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>279000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>263000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>291000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>263000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>269100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>257600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>268800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>250000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>516900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>251300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>268300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>235500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>352200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>266000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>331100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>292300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>440700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>296600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>298600</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>337900</v>
+      </c>
+      <c r="E10" s="3">
         <v>373300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>317400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>329900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>358000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>338600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>364300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>383400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>364200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>369800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>368100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>376700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>373800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>383000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>357300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>732900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>361300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>348000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>311700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>413400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>281200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>389400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>367000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1643200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>363100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>380900</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1093,100 +1106,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E12" s="3">
         <v>26700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>51700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>43500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>34700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>35400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>36300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>139100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>43300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>36000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>42300</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1277,89 +1294,92 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>12800</v>
+        <v>10300</v>
       </c>
       <c r="E14" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1161100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6900</v>
       </c>
-      <c r="H14" s="3">
-        <v>268700</v>
-      </c>
       <c r="I14" s="3">
+        <v>272000</v>
+      </c>
+      <c r="J14" s="3">
         <v>39100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>58800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>57400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>39100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>51900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1950500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1369,38 +1389,41 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E15" s="3">
         <v>27800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>32900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>33500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1461,8 +1484,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1492,192 +1518,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>567600</v>
+      </c>
+      <c r="E17" s="3">
         <v>593300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>578500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>626800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>568600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>577200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>541200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>569900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>550800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>572800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>556600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>580600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>539900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>605700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>525600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1071400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>517500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>542800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>485600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>857200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>572200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>642500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>580600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>735600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>614800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>115300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>598100</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E18" s="3">
         <v>59600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>55000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>68400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>90100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>92500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>76400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>88000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>74500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>65200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>91500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>81700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>178400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>95100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>73500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>61600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-91600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-25000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>78000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>78700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1348300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>44900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>81400</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1710,40 +1743,41 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>800</v>
-      </c>
       <c r="I20" s="3">
-        <v>-200</v>
+        <v>-2500</v>
       </c>
       <c r="J20" s="3">
         <v>-200</v>
       </c>
       <c r="K20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>300</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
@@ -1752,233 +1786,239 @@
         <v>300</v>
       </c>
       <c r="P20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
       </c>
       <c r="W20" s="3">
+        <v>200</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1500</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>87000</v>
+        <v>76500</v>
       </c>
       <c r="E21" s="3">
+        <v>88500</v>
+      </c>
+      <c r="F21" s="3">
         <v>51700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>87200</v>
       </c>
-      <c r="H21" s="3">
-        <v>100500</v>
-      </c>
       <c r="I21" s="3">
+        <v>103800</v>
+      </c>
+      <c r="J21" s="3">
         <v>123100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>126200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>113100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>125900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>110500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>100600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>123100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>79300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>112000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>240900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>126700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>105200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>96400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-26500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>109300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>156200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>318700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>77300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>160300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E22" s="3">
         <v>9900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>31600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17800</v>
-      </c>
-      <c r="W22" s="3">
-        <v>3300</v>
       </c>
       <c r="X22" s="3">
         <v>3300</v>
       </c>
       <c r="Y22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>99400</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>115300</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -1986,192 +2026,201 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E23" s="3">
         <v>36500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>35300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-215000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>35800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>68600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>55700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>75700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>63200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>59100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>85900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>37200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>69900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>147400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>77400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>50800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>38400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-109200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-28200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>74600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>78700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>231800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>45000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="3">
         <v>82900</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>35300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-14500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-10300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-40300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-37000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-11000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>15700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>115300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18800</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2262,192 +2311,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-217400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>51900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>43800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>70400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>42500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>80200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>140800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>61800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>91100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-72200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-17200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>56100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>62100</v>
       </c>
       <c r="Z26" s="3">
         <v>62100</v>
       </c>
       <c r="AA26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>37900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>154600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>64100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-217400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>51900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>43800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>70400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>42500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>80200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>140800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>61800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>91100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-72200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>56100</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>62100</v>
       </c>
       <c r="Z27" s="3">
         <v>62100</v>
       </c>
       <c r="AA27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>37900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>154600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>64100</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2538,8 +2596,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,40 +2632,40 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-2000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>2600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>4500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>43300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>12700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>21000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>9900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>17300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>12000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-38500</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2630,8 +2691,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2722,8 +2786,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2814,40 +2881,43 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-800</v>
-      </c>
       <c r="I32" s="3">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="J32" s="3">
         <v>200</v>
       </c>
       <c r="K32" s="3">
+        <v>200</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-300</v>
       </c>
       <c r="N32" s="3">
         <v>-300</v>
@@ -2856,150 +2926,156 @@
         <v>-300</v>
       </c>
       <c r="P32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
       </c>
       <c r="W32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1017100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-217400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>51900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>47600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>47100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>85800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>92900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>161800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>71700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>108400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-110700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>56100</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>62100</v>
       </c>
       <c r="Z33" s="3">
         <v>62100</v>
       </c>
       <c r="AA33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>37900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>154600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>64100</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3090,197 +3166,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-217400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>51900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>47600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>47100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>85800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>92900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>161800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>71700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>108400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-110700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>56100</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>62100</v>
       </c>
       <c r="Z35" s="3">
         <v>62100</v>
       </c>
       <c r="AA35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>37900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>154600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>64100</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45562</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45471</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45380</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45198</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44743</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44652</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44470</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44379</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44288</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44106</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44015</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43924</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43644</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43553</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43371</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3313,8 +3398,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3347,80 +3433,81 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1077300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1069100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>991300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1036200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>948500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>940000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>824200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>651700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>585200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>606900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>568500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>523100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1078300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1073600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>638800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>553900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>441200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>888900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>700800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>822400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>353600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>211200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>193200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3439,8 +3526,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3531,83 +3621,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>393100</v>
+      </c>
+      <c r="E43" s="3">
         <v>363000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>392100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>380600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>413000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>407500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>417100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>415200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>401800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>393500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>392200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>372800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>342600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>331900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>307400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>355000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>358100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>361000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>365400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>306400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>365900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>443600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>456400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3602200</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,83 +3716,86 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>261300</v>
+      </c>
+      <c r="E44" s="3">
         <v>241000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>265600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>263800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>267400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>258800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>278800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>297000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>307200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>291300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>286000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>280400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>263800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>274300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>311500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>283200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>266900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>257500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>280800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>312300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>277900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>278400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1624300</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3715,8 +3811,11 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3726,12 +3825,12 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3744,54 +3843,54 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>123400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>114000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>206400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>207600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>166500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>545900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>81300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>80800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>73700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>92500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>108100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>82400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>69200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>50500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1328700</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3807,83 +3906,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1849700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1788300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1797000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1821900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1771900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1743700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1640700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1488900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1414300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1424600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1366000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1388300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1908900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1835800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1766400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1301700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1163300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1590500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1416200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1517700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1114200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1001900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>978500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6009000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3899,13 +4001,16 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>27100</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -3928,8 +4033,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3958,32 +4063,32 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3">
         <v>22300</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="3">
         <v>4938800</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -3991,83 +4096,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>418400</v>
+      </c>
+      <c r="E48" s="3">
         <v>419800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>433200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>415800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>431500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>434700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>430600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>429700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>430500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>425400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>409300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>394600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>391200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>392200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>416900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>457800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>451200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>468300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>473900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>483200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>482600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>490400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>484900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17317700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4083,83 +4191,86 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2953600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2911800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3029900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2981800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4178500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4246200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4459600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4536900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4571900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4583300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4463400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4465700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4097300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4178400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4204600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4574800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4580400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4689900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4642900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4589100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4551100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4591600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4574300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>623900</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4286,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4267,8 +4381,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4359,83 +4476,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>230600</v>
+        <v>217600</v>
       </c>
       <c r="E52" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F52" s="3">
         <v>250600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>218600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>174400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>180500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>152900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>151700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>158300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>153700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>173200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>212400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>174900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>167800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>174100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>147000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>127000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>127300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>72700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>75200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>70700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>74400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>80700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>626800</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4451,8 +4571,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4543,83 +4666,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5466400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5350500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5510700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5438100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6556300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6605100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6683800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6607200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6575000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6587000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6411900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6461000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6572300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6574200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6562000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6481300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6321900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6876000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6605700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6665200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6240900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6158300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6118400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>154600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4635,8 +4761,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4669,8 +4798,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4703,80 +4833,81 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>163500</v>
+      </c>
+      <c r="E57" s="3">
         <v>174600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>172100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>172400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>174700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>179500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>168600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>176800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>186800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>228300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>190000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>182700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>180600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>185800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>171000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>209400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>204600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>235100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>161100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>130900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>194800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>208000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>181400</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4795,80 +4926,83 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E58" s="3">
         <v>150500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>150200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>148000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>145600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>144500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>540000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>539200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>510000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>579300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>508600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>507800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>432400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>426700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>421500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>416400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>886800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>253500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>152000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4887,83 +5021,86 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>359300</v>
+      </c>
+      <c r="E59" s="3">
         <v>317200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>314200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>301200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>286000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>257900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>236700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>250600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>252700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>498400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>489000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>564900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>567300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>590000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>671500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>532300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>515300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>562800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>514000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>445800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>410600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>497300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>427300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5070100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,83 +5116,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>873300</v>
+      </c>
+      <c r="E60" s="3">
         <v>878700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>865500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>821400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>781300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>780800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>746800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1150800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1149600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1236700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1258300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1256200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1255700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1208200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1269200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1163200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1136300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1684700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>678900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>830200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>608900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>709200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>760700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5071,83 +5211,86 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1030500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1397200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1423000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1492500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1498000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1508000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1493300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>992400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>995100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>870700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>851600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>864100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>876900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>883400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>887800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>893200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>892200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>907700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1755500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1722200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1546700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1321000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1304500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>25000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5163,83 +5306,86 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>475300</v>
+      </c>
+      <c r="E62" s="3">
         <v>89800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>103800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>104100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>103700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>103900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>127100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>128100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>126800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>272700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>344100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>324700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>408800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>424600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>457900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>556000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>546100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>562600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>611500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>616900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>599000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>585300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>539200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>329200</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5255,8 +5401,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5347,8 +5496,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5439,8 +5591,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5531,80 +5686,83 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2430300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2415700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2438200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2461400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2416000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2431200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2390600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2296200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2296000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2380100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2454000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2445000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2541400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2516600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2615300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2612800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2575000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3155400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3048100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3171800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2757200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2618100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2607100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5623,8 +5781,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5657,8 +5818,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5749,8 +5911,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5841,8 +6006,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5933,8 +6101,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6025,80 +6196,83 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-469400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-487400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-488600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-496800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>654800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>631200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>848600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>827100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>775200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>731400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>657900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>610300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>563200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>466900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>381100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>288200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>198100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>126400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>75900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>93100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6117,8 +6291,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6209,8 +6386,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6301,8 +6481,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6393,80 +6576,83 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3036100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2934800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3072500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2976700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4140300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4173900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4293200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4311000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4279000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4206900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3957900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4016000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4030900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4057600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3946700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3868500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3746900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3720600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3557600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3493400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3483700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3540200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3511300</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6485,8 +6671,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6577,197 +6766,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45562</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45471</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45380</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45198</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44743</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44652</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44470</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44379</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44288</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44106</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44015</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43924</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43644</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43553</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43371</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-217400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>51900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>47600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>47100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>85800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>92900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>161800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>71700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>108400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-110700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>56100</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>62100</v>
       </c>
       <c r="Z81" s="3">
         <v>62100</v>
       </c>
       <c r="AA81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>37900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>154600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>64100</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6800,100 +6998,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E83" s="3">
         <v>9200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>14200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>35700</v>
       </c>
       <c r="M83" s="3">
         <v>35700</v>
       </c>
       <c r="N83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="O83" s="3">
         <v>35100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>31600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>30100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>61900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>33100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>34600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>64900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>77300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>21400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>77400</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6984,8 +7186,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7076,8 +7281,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7168,8 +7376,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7260,8 +7471,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7352,100 +7566,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>132400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>93100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>102000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>95500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>75100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>110300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>136000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>88300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>137300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>193400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>148100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-57600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-62300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>187000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>281300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-61800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>210500</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7478,91 +7698,92 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-21400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>8900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-55200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -7570,8 +7791,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7662,8 +7886,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7754,100 +7981,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-69700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-591600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>288600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>15300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>58900</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7880,8 +8113,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7909,8 +8143,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7972,8 +8206,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8064,8 +8301,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8156,8 +8396,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8248,86 +8491,89 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>114500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-68300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>73700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-463100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-469600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-244400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>733100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>258500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-148100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3">
         <v>24300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8340,85 +8586,88 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E101" s="3">
         <v>23100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-9200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>12400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>13600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-15700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-9900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
       </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
@@ -8432,85 +8681,88 @@
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E102" s="3">
         <v>77800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-44900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>87700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>115800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>172500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>66500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>38400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>45400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-555200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>434800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>84900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-335000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-447700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>188100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-121600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>611200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>142400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
       </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
@@ -8522,6 +8774,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,424 +656,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E7" s="2">
         <v>45744</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45562</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45471</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45380</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45198</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44743</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44652</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44470</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44379</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44288</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44106</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44015</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43924</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43644</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43553</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43371</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>682100</v>
+      </c>
+      <c r="E8" s="3">
         <v>616900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>652900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>601000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>633100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>623600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>645600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>631300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>662400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>627200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>660800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>631100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>645800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>631400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>651800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>607300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1249800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>612600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>616300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>547200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>765600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>547200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>720500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>659300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2083900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>659700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>679500</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>311900</v>
+      </c>
+      <c r="E9" s="3">
         <v>279000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>279600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>283600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>303200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>265600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>307000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>267000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>279000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>263000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>291000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>263000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>269100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>257600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>268800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>250000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>516900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>251300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>268300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>235500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>352200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>266000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>331100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>292300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>440700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>296600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>298600</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>370200</v>
+      </c>
+      <c r="E10" s="3">
         <v>337900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>373300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>317400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>329900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>358000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>338600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>364300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>383400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>364200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>369800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>368100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>376700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>373800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>383000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>357300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>732900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>361300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>348000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>311700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>413400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>281200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>389400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>367000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1643200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>363100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>380900</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,103 +1120,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E12" s="3">
         <v>25300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>51700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>25800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>43500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>34700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>35400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>36300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>139100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>43300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>36000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>42300</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1297,92 +1314,95 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E14" s="3">
         <v>10300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>14300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1161100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>272000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>39100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>58800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>15200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>57400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>39100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>51900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1950500</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1392,41 +1412,44 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E15" s="3">
         <v>27900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>34000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>32100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>33500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1487,8 +1510,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1519,198 +1545,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>631300</v>
+      </c>
+      <c r="E17" s="3">
         <v>567600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>593300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>578500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>626800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>568600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>577200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>541200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>569900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>550800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>572800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>556600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>580600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>539900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>605700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>525600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1071400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>517500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>542800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>485600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>857200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>572200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>642500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>580600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>735600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>614800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>115300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>598100</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E18" s="3">
         <v>49300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>59600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>22500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>55000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>68400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>90100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>92500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>76400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>88000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>74500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>65200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>91500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>81700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>178400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>95100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>73500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>61600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-91600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>78000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>78700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1348300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>44900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>81400</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1744,43 +1777,44 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
       </c>
       <c r="L20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>300</v>
       </c>
       <c r="O20" s="3">
         <v>300</v>
@@ -1789,239 +1823,245 @@
         <v>300</v>
       </c>
       <c r="Q20" s="3">
+        <v>300</v>
+      </c>
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
       </c>
       <c r="W20" s="3">
         <v>200</v>
       </c>
       <c r="X20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3">
         <v>1500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E21" s="3">
         <v>76500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>88500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>87200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>103800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>123100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>126200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>113100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>125900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>110500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>100600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>123100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>79300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>112000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>240900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>126700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>105200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>96400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-26500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>109300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>156200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>318700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>77300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>160300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="3">
         <v>9300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>31600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17800</v>
-      </c>
-      <c r="X22" s="3">
-        <v>3300</v>
       </c>
       <c r="Y22" s="3">
         <v>3300</v>
       </c>
       <c r="Z22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>99400</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>115300</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
@@ -2029,198 +2069,207 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E23" s="3">
         <v>29000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>36500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>35300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-215000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>35800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>68600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>55700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>75700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>63200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>85900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>37200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>69900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>147400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>77400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>50800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-109200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-28200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>74600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>78700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>231800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>45000</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE23" s="3">
         <v>82900</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E24" s="3">
         <v>11000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>35300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-14500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>16700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-10300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-40300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-37000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>15700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>115300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18800</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2314,198 +2363,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E26" s="3">
         <v>18000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-217400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>51900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>43800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>70400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>42500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>80200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>140800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>61800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>91100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-72200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>56100</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>62100</v>
       </c>
       <c r="AA26" s="3">
         <v>62100</v>
       </c>
       <c r="AB26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>37900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>154600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>64100</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E27" s="3">
         <v>18000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-217400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>43800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>49600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>70400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>42500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>80200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>140800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>61800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>91100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-72200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>56100</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>62100</v>
       </c>
       <c r="AA27" s="3">
         <v>62100</v>
       </c>
       <c r="AB27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>37900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>154600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>64100</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2599,8 +2657,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,40 +2696,40 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-2000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>2600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>4500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>43300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>12700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>21000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>9900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>17300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>12000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-38500</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2694,8 +2755,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2789,8 +2853,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2884,43 +2951,46 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
       </c>
       <c r="L32" s="3">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-300</v>
       </c>
       <c r="O32" s="3">
         <v>-300</v>
@@ -2929,153 +2999,159 @@
         <v>-300</v>
       </c>
       <c r="Q32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
       </c>
       <c r="W32" s="3">
         <v>-200</v>
       </c>
       <c r="X32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1017100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E33" s="3">
         <v>18000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-217400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>51900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>43800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>73500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>47600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>47100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>85800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>92900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>161800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>71700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>108400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-110700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>56100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>62100</v>
       </c>
       <c r="AA33" s="3">
         <v>62100</v>
       </c>
       <c r="AB33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>37900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>154600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>64100</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3169,203 +3245,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E35" s="3">
         <v>18000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-217400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>51900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>43800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>73500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>47600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>47100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>85800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>92900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>161800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>71700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>108400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-110700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>56100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>62100</v>
       </c>
       <c r="AA35" s="3">
         <v>62100</v>
       </c>
       <c r="AB35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>37900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>154600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>64100</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E38" s="2">
         <v>45744</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45562</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45471</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45380</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45198</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44743</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44652</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44470</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44379</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44288</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44106</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44015</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43924</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43644</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43553</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43371</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3399,8 +3484,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3434,83 +3520,84 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1110600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1077300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1069100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>991300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1036200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>948500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>940000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>824200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>651700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>585200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>606900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>568500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>523100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1078300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1073600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>638800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>553900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>441200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>888900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>700800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>822400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>353600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>211200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>193200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,8 +3616,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3624,86 +3714,89 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>422800</v>
+      </c>
+      <c r="E43" s="3">
         <v>393100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>363000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>392100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>380600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>413000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>407500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>417100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>415200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>401800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>393500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>392200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>372800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>342600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>331900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>307400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>355000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>358100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>361000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>365400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>306400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>365900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>443600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>456400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3602200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3719,86 +3812,89 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>281900</v>
+      </c>
+      <c r="E44" s="3">
         <v>261300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>241000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>265600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>263800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>267400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>258800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>278800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>297000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>307200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>300800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>291300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>286000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>280400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>263800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>274300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>311500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>283200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>266900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>257500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>280800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>312300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>277900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>278400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1624300</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3814,8 +3910,11 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3828,12 +3927,12 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,54 +3945,54 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>123400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>114000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>206400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>207600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>166500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>545900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>81300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>80800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>73700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>92500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>108100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>82400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>69200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>50500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1328700</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3909,86 +4008,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1934900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1849700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1788300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1797000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1821900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1771900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1743700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1640700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1488900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1414300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1424600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1366000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1388300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1908900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1835800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1766400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1301700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1163300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1590500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1416200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1517700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1114200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1001900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>978500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6009000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,25 +4106,28 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E47" s="3">
         <v>27100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+      <c r="H47" s="3">
+        <v>26700</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -4036,8 +4141,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4066,32 +4171,32 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
         <v>22300</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3">
         <v>4938800</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -4099,86 +4204,89 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>428900</v>
+      </c>
+      <c r="E48" s="3">
         <v>418400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>419800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>433200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>415800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>431500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>434700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>430600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>429700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>430500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>425400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>409300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>394600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>391200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>392200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>416900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>457800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>451200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>468300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>473900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>483200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>482600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>490400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>484900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17317700</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4194,86 +4302,89 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3035700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2953600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2911800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3029900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2981800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4178500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4246200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4459600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4536900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4571900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4583300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4463400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4465700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4097300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4178400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4204600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4574800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4580400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4689900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4642900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4589100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4551100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4591600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4574300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>623900</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4289,8 +4400,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4384,8 +4498,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4479,86 +4596,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>236200</v>
+      </c>
+      <c r="E52" s="3">
         <v>217600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>44000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>250600</v>
       </c>
-      <c r="G52" s="3">
-        <v>218600</v>
-      </c>
       <c r="H52" s="3">
+        <v>191900</v>
+      </c>
+      <c r="I52" s="3">
         <v>174400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>180500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>152900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>151700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>158300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>153700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>173200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>212400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>174900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>167800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>174100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>147000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>127000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>127300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>72700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>75200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>70700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>74400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>80700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>626800</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4574,8 +4694,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4669,86 +4792,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5664400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5466400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5350500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5510700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5438100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6556300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6605100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6683800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6607200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6575000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6587000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6411900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6461000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6572300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6574200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6562000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6481300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6321900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6876000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6605700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6665200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6240900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6158300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6118400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>154600</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4764,8 +4890,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4799,8 +4928,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4834,83 +4964,84 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>171800</v>
+      </c>
+      <c r="E57" s="3">
         <v>163500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>174600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>172100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>172400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>174700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>179500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>168600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>176800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>186800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>228300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>190000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>182700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>180600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>185800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>171000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>209400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>204600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>235100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>161100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>130900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>194800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>208000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>181400</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4929,83 +5060,86 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E58" s="3">
         <v>151000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>150500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>152000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>150200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>148000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>145600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>144500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>540000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>539200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>510000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>579300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>508600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>507800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>432400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>426700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>421500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>416400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>886800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>253500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>152000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5024,86 +5158,89 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>370100</v>
+      </c>
+      <c r="E59" s="3">
         <v>359300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>317200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>314200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>301200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>286000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>257900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>236700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>250600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>252700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>498400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>489000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>564900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>567300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>590000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>671500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>532300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>515300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>562800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>514000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>445800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>410600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>497300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>427300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5070100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5119,86 +5256,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>793900</v>
+      </c>
+      <c r="E60" s="3">
         <v>873300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>878700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>865500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>821400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>781300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>780800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>746800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1150800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1149600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1236700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1258300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1256200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1255700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1208200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1269200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1163200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1136300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1684700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>678900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>830200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>608900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>709200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>760700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17300</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5214,86 +5354,89 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1030500</v>
+        <v>1560100</v>
       </c>
       <c r="E61" s="3">
+        <v>1409500</v>
+      </c>
+      <c r="F61" s="3">
         <v>1397200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1423000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1492500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1498000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1508000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1493300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>992400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>995100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>870700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>851600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>864100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>876900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>883400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>887800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>893200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>892200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>907700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1755500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1722200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1546700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1321000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1304500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5309,86 +5452,89 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>475300</v>
+        <v>114800</v>
       </c>
       <c r="E62" s="3">
+        <v>96300</v>
+      </c>
+      <c r="F62" s="3">
         <v>89800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>103800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>104100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>103700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>103900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>127100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>128100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>126800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>272700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>344100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>324700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>408800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>424600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>457900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>556000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>546100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>562600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>611500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>616900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>599000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>585300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>539200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>329200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5404,8 +5550,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5499,8 +5648,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5594,8 +5746,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5689,83 +5844,86 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2525400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2430300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2415700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2438200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2461400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2416000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2431200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2390600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2296200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2296000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2380100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2454000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2445000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2541400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2516600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2615300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2612800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2575000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3155400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3048100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3171800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2757200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2618100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2607100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5784,8 +5942,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5819,8 +5980,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5914,8 +6076,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6009,8 +6174,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6104,8 +6272,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6199,83 +6370,86 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-443000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-469400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-487400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-488600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-496800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>654800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>631200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>848600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>827100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>775200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>731400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>657900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>610300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>563200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>466900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>381100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>288200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>198100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>126400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-17600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>75900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>93100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6294,8 +6468,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6389,8 +6566,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6484,8 +6664,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6579,83 +6762,86 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3139000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3036100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2934800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3072500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2976700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4140300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4173900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4293200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4311000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4279000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4206900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3957900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4016000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4030900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4057600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3946700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3868500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3746900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3720600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3557600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3493400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3483700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3540200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3511300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6674,8 +6860,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6769,203 +6958,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E80" s="2">
         <v>45744</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45562</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45471</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45380</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45198</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44743</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44652</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44470</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44379</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44288</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44106</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44015</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43924</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43644</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43553</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43371</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E81" s="3">
         <v>18000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-217400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>51900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>43800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>73500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>47600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>47100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>85800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>92900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>161800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>71700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>108400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-110700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>56100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>62100</v>
       </c>
       <c r="AA81" s="3">
         <v>62100</v>
       </c>
       <c r="AB81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>37900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>154600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>64100</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6999,103 +7197,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E83" s="3">
         <v>9500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>14200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>35700</v>
       </c>
       <c r="N83" s="3">
         <v>35700</v>
       </c>
       <c r="O83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="P83" s="3">
         <v>35100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>31300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>31600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>61900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>33100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>34600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>31400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>77300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>21400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>77400</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7189,8 +7391,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7284,8 +7489,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7379,8 +7587,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7474,8 +7685,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7569,103 +7783,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>132400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>70700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>93100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>40300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>102000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>95500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>75100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>110300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>136000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>88300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>137300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>193400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>148100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-57600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-62300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>187000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>281300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-61800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>210500</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7699,94 +7919,95 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-17500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>8900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-55200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -7794,8 +8015,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7889,8 +8113,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7984,103 +8211,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-69700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-591600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>288600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-54400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>15300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15300</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>58900</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8114,8 +8347,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8146,8 +8380,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8209,8 +8443,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8304,8 +8541,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8399,8 +8639,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8494,89 +8737,92 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>114500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-68300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>73700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-463100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-469600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-244400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>733100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>258500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-148100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3">
         <v>24300</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8589,88 +8835,91 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>23100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-9200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>12400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>10800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-15700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-9900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
@@ -8684,88 +8933,91 @@
       <c r="AG101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E102" s="3">
         <v>8200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-44900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>87700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>115800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>172500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>66500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>45400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-555200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>434800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>84900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-335000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-447700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>188100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-121600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>611200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>142400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
       </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
@@ -8777,6 +9029,9 @@
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,450 +656,462 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45835</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45744</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45562</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45471</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45380</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45198</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44743</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44652</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44470</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44379</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44288</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44106</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44015</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43924</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43644</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43553</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43371</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>750600</v>
+      </c>
+      <c r="E8" s="3">
         <v>669900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>682100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>616900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>652900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>601000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>633100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>623600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>645600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>631300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>662400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>627200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>660800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>631100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>645800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>631400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>651800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>607300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1249800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>612600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>616300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>547200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>765600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>547200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>720500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>659300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2083900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>659700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>679500</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>337500</v>
+      </c>
+      <c r="E9" s="3">
         <v>294800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>311900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>279000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>279600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>303200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>265600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>307000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>267000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>279000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>263000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>291000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>263000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>269100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>257600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>268800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>250000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>516900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>251300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>268300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>235500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>352200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>266000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>331100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>292300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>440700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>296600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>298600</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>413100</v>
+      </c>
+      <c r="E10" s="3">
         <v>375100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>370200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>337900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>373300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>317400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>329900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>358000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>338600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>364300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>383400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>364200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>369800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>368100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>376700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>373800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>383000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>357300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>732900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>361300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>348000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>311700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>413400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>281200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>389400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>367000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1643200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>363100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>380900</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1135,109 +1147,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>28300</v>
+        <v>32100</v>
       </c>
       <c r="E12" s="3">
         <v>28300</v>
       </c>
       <c r="F12" s="3">
+        <v>28300</v>
+      </c>
+      <c r="G12" s="3">
         <v>25300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>51700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>25800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>20000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>43500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>34700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>35400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>36300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>139100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>43300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>36000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>42300</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,98 +1353,101 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E14" s="3">
         <v>7300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1161100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>272000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>39100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>58800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>57400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>39100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>51900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1950500</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1438,47 +1457,50 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E15" s="3">
         <v>29200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>33500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>36400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1539,8 +1561,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1573,210 +1598,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>670000</v>
+      </c>
+      <c r="E17" s="3">
         <v>605100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>631300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>567600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>593300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>578500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>626800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>568600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>577200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>541200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>569900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>550800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>572800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>556600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>580600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>539900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>605700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>525600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1071400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>517500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>542800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>485600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>857200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>572200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>642500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>580600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>735600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>614800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>115300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>598100</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E18" s="3">
         <v>64800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>50800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>49300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>59600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>22500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>55000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>68400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>90100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>92500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>76400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>88000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>74500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>65200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>91500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>46100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>81700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>178400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>95100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>73500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>61600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-91600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>78000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>78700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1348300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>44900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>81400</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1812,49 +1844,50 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-200</v>
       </c>
       <c r="M20" s="3">
         <v>-200</v>
       </c>
       <c r="N20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>300</v>
       </c>
       <c r="Q20" s="3">
         <v>300</v>
@@ -1863,251 +1896,257 @@
         <v>300</v>
       </c>
       <c r="S20" s="3">
+        <v>300</v>
+      </c>
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3">
         <v>1500</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E21" s="3">
         <v>95400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>83000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>76500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>88500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>51700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>87200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>103800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>123100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>126200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>113100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>125900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>110500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>100600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>123100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>79300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>112000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>240900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>126700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>105200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>96400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>109300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>156200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>318700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>77300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3">
         <v>160300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E22" s="3">
         <v>9000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>31600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17800</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>3300</v>
       </c>
       <c r="AA22" s="3">
         <v>3300</v>
       </c>
       <c r="AB22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>99400</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>115300</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
+      <c r="AG22" s="3">
+        <v>0</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
@@ -2115,210 +2154,219 @@
       <c r="AI22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E23" s="3">
         <v>49900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>40700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>35300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-215000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>35800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>68600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>55700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>75700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>63200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>85900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>37200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>69900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>147400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>77400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>50800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>38400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-109200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-28200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>74600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>78700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>231800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>45000</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="3">
         <v>82900</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E24" s="3">
         <v>80200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>35300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-14500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-10300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-40300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-37000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>115300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18800</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2418,210 +2466,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-217400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>51900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>43800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>73500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>44500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>70400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>42500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>80200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>140800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>61800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>91100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-72200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>56100</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>62100</v>
       </c>
       <c r="AC26" s="3">
         <v>62100</v>
       </c>
       <c r="AD26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>37900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>154600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>64100</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-217400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>51900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>43800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>73500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>49600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>44500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>70400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>42500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>80200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>140800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>61800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>91100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>23600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-72200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>56100</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>62100</v>
       </c>
       <c r="AC27" s="3">
         <v>62100</v>
       </c>
       <c r="AD27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>37900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>154600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>64100</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2721,8 +2778,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,40 +2823,40 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>2600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>4500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>43300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>12700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>21000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>9900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>17300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>12000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-38500</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2822,8 +2882,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2923,8 +2986,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3024,49 +3090,52 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>200</v>
       </c>
       <c r="M32" s="3">
         <v>200</v>
       </c>
       <c r="N32" s="3">
+        <v>200</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-300</v>
       </c>
       <c r="Q32" s="3">
         <v>-300</v>
@@ -3075,159 +3144,165 @@
         <v>-300</v>
       </c>
       <c r="S32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1017100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-217400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>51900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>43800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>73500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>47600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>47100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>85800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>92900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>161800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>71700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>108400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-110700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>56100</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>62100</v>
       </c>
       <c r="AC33" s="3">
         <v>62100</v>
       </c>
       <c r="AD33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>37900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>154600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>64100</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3327,215 +3402,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-217400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>51900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>43800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>73500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>47600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>47100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>85800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>92900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>161800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>71700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>108400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-110700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>56100</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>62100</v>
       </c>
       <c r="AC35" s="3">
         <v>62100</v>
       </c>
       <c r="AD35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>37900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>154600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>64100</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45835</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45744</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45562</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45471</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45380</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45198</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44743</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44652</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44470</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44379</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44288</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44106</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44015</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43924</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43644</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43553</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43371</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3571,8 +3655,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3608,89 +3693,90 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1211700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1133900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1110600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1077300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1069100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>991300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1036200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>948500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>940000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>824200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>651700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>585200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>606900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>568500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>523100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1078300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1073600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>638800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>553900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>441200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>888900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>700800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>822400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>353600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>211200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>193200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,8 +3795,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3810,92 +3899,95 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>429600</v>
+      </c>
+      <c r="E43" s="3">
         <v>405900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>422800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>393100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>363000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>392100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>380600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>413000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>407500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>417100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>415200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>401800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>393500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>392200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>372800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>342600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>331900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>307400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>355000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>358100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>361000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>365400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>306400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>365900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>443600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>456400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3602200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3911,92 +4003,95 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>288100</v>
+      </c>
+      <c r="E44" s="3">
         <v>290800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>281900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>261300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>241000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>265600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>263800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>267400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>258800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>278800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>297000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>307200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>300800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>291300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>286000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>280400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>263800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>274300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>311500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>283200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>266900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>257500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>280800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>312300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>277900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>278400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1624300</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4012,8 +4107,11 @@
       <c r="AI44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4032,12 +4130,12 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4050,54 +4148,54 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>123400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>114000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>206400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>207600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>166500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>545900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>81300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>80800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>73700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>92500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>108100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>82400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>69200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>50500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1328700</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,92 +4211,95 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2026600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1948300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1934900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1849700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1788300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1797000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1821900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1771900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1743700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1640700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1488900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1414300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1424600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1366000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1388300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1908900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1835800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1766400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1301700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1163300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1590500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1416200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1517700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1114200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1001900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>978500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6009000</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,32 +4315,35 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>28700</v>
+        <v>28800</v>
       </c>
       <c r="E47" s="3">
         <v>28700</v>
       </c>
       <c r="F47" s="3">
+        <v>28700</v>
+      </c>
+      <c r="G47" s="3">
         <v>27100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="H47" s="3">
+        <v>26400</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>26700</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4356,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4282,32 +4386,32 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="3">
         <v>22300</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD47" s="3">
         <v>4938800</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH47" s="3">
         <v>0</v>
@@ -4315,92 +4419,95 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>438900</v>
+      </c>
+      <c r="E48" s="3">
         <v>436400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>428900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>418400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>419800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>433200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>415800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>431500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>434700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>430600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>429700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>430500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>425400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>409300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>394600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>391200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>392200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>416900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>457800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>451200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>468300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>473900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>483200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>482600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>490400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>484900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17317700</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4416,92 +4523,95 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2985400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3008500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3035700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2953600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2911800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3029900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2981800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4178500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4246200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4459600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4536900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4571900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4583300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4463400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4465700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4097300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4178400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4204600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4574800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4580400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4689900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4642900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4589100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4551100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4591600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4574300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>623900</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4517,8 +4627,11 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4618,8 +4731,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4719,92 +4835,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E52" s="3">
         <v>220600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>236200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>217600</v>
       </c>
-      <c r="G52" s="3">
-        <v>44000</v>
-      </c>
       <c r="H52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="I52" s="3">
         <v>250600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>191900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>174400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>180500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>152900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>151700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>158300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>153700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>173200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>212400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>174900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>167800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>174100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>147000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>127000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>127300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>72700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>75200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>70700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>74400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>80700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>626800</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4820,8 +4939,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4921,92 +5043,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5679000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5642500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5664400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5466400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5350500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5510700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5438100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6556300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6605100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6683800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6607200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6575000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6587000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6411900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6461000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6572300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6574200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6562000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6481300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6321900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6876000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6605700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6665200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6240900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6158300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6118400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>154600</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5022,8 +5147,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5059,8 +5187,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5096,89 +5225,90 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>191600</v>
+      </c>
+      <c r="E57" s="3">
         <v>156000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>171800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>163500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>174600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>172100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>172400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>174700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>179500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>168600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>176800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>186800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>228300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>190000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>182700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>180600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>185800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>171000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>209400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>204600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>235100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>161100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>130900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>194800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>208000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>181400</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5197,89 +5327,92 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E58" s="3">
         <v>39200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>151000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>150500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>152000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>150200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>148000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>145600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>144500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>540000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>539200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>510000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>579300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>508600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>507800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>432400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>426700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>421500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>416400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>886800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>253500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>152000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5298,92 +5431,95 @@
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>359100</v>
+      </c>
+      <c r="E59" s="3">
         <v>384900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>370100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>359300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>317200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>314200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>301200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>286000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>257900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>236700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>250600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>252700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>498400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>489000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>564900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>567300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>590000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>671500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>532300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>515300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>562800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>514000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>445800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>410600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>497300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>427300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5070100</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5399,92 +5535,95 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>852600</v>
+      </c>
+      <c r="E60" s="3">
         <v>821700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>793900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>873300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>878700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>865500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>821400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>781300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>780800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>746800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1150800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1149600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1236700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1258300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1256200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1255700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1208200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1269200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1163200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1136300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1684700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>678900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>830200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>608900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>709200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>760700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17300</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5500,92 +5639,95 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1558700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1562900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1560100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1409500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1397200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1423000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1492500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1498000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1508000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1493300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>992400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>995100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>870700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>851600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>864100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>876900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>883400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>887800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>893200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>892200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>907700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1755500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1722200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1546700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1321000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1304500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5601,92 +5743,95 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E62" s="3">
         <v>112500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>114800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>96300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>89800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>103800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>104100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>103700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>103900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>127100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>128100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>126800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>272700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>344100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>324700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>408800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>424600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>457900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>556000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>546100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>562600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>611500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>616900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>599000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>585300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>539200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>329200</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5702,8 +5847,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5803,8 +5951,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5904,8 +6055,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6005,89 +6159,92 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2572700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2554300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2525400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2430300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2415700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2438200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2461400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2416000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2431200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2390600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2296200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2296000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2380100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2454000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2445000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2541400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2516600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2615300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2612800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2575000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3155400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3048100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3171800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2757200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2618100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2607100</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6106,8 +6263,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6143,8 +6303,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6244,8 +6405,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6345,8 +6509,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6446,8 +6613,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6547,89 +6717,92 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-440400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-473300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-443000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-469400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-487400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-488600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-496800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>654800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>631200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>848600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>827100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>775200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>731400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>657900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>610300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>563200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>466900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>381100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>288200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>198100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>126400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>75900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>93100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>37000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6648,8 +6821,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6749,8 +6925,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6850,8 +7029,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6951,89 +7133,92 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3106300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3088200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3139000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3036100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2934800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3072500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2976700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4140300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4173900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4293200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4311000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4279000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4206900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3957900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4016000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4030900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4057600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3946700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3868500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3746900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3720600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3557600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3493400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3483700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3540200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3511300</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7052,8 +7237,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7153,215 +7341,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45835</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45744</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45562</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45471</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45380</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45198</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44743</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44652</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44470</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44379</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44288</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44106</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44015</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43924</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43644</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43553</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43371</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-217400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>51900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>43800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>73500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>47600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>47100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>85800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>92900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>161800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>71700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>108400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-110700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>56100</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>62100</v>
       </c>
       <c r="AC81" s="3">
         <v>62100</v>
       </c>
       <c r="AD81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>37900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>154600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>64100</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7397,109 +7594,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E83" s="3">
         <v>10500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>14200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>35700</v>
       </c>
       <c r="P83" s="3">
         <v>35700</v>
       </c>
       <c r="Q83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="R83" s="3">
         <v>35100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>31300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>61900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>33100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>34600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>64900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>77300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>77400</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7599,8 +7800,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7700,8 +7904,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7801,8 +8008,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7902,8 +8112,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8003,109 +8216,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E89" s="3">
         <v>78700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>88700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>132400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>70700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>93100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>102000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>95500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>75100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>110300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>46700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>136000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>88300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>137300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>193400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>148100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-62300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>187000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>281300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-61800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>210500</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8141,100 +8360,101 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-17500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-28500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-21400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>8900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-55200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
@@ -8242,8 +8462,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8343,8 +8566,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8444,109 +8670,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-69700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-591600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>288600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-54400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>15300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>58900</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8582,8 +8814,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8620,8 +8853,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8683,8 +8916,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8784,8 +9020,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8885,8 +9124,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8986,95 +9228,98 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-41700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-86400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>114500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-68300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>73700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-463100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-469600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-244400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>733100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>258500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-148100</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE100" s="3">
         <v>24300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9087,94 +9332,97 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="E101" s="3">
         <v>15500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-18500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>23100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-9200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>12400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>13600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>10800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3" t="s">
-        <v>3</v>
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>3</v>
@@ -9188,94 +9436,97 @@
       <c r="AI101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E102" s="3">
         <v>23300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>33300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>77800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-44900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>87700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>115800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>172500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>66500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>45400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-555200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>434800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>84900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-335000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-447700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>188100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-121600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>611200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>142400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
+      <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
       </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
@@ -9287,6 +9538,9 @@
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,462 +656,475 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45835</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45744</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45562</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45471</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45380</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45198</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44743</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44652</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44470</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44379</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44288</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44106</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44015</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43924</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43644</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43553</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43371</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>705500</v>
+      </c>
+      <c r="E8" s="3">
         <v>750600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>669900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>682100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>616900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>652900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>601000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>633100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>623600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>645600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>631300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>662400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>627200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>660800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>631100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>645800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>631400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>651800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>607300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1249800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>612600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>616300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>547200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>765600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>547200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>720500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>659300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2083900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>659700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>679500</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>312300</v>
+      </c>
+      <c r="E9" s="3">
         <v>337500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>294800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>311900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>279000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>279600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>283600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>303200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>265600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>307000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>267000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>279000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>263000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>291000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>263000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>269100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>257600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>268800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>250000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>516900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>251300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>268300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>235500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>352200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>266000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>331100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>292300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>440700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>296600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>298600</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>393200</v>
+      </c>
+      <c r="E10" s="3">
         <v>413100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>375100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>370200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>337900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>373300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>317400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>329900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>358000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>338600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>364300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>383400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>364200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>369800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>368100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>376700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>373800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>383000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>357300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>732900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>361300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>348000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>311700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>413400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>281200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>389400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>367000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1643200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>363100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>380900</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1148,112 +1161,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="3">
         <v>32100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>28300</v>
       </c>
       <c r="F12" s="3">
         <v>28300</v>
       </c>
       <c r="G12" s="3">
+        <v>28300</v>
+      </c>
+      <c r="H12" s="3">
         <v>25300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>51700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>25800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>23200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>43500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>34700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>35400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>36300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>139100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>43300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>36000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>42300</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,101 +1373,104 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E14" s="3">
         <v>7200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1161100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>272000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>39100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>58800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>15200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>7800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>57400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>39100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>51900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="3">
         <v>1950500</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1460,50 +1480,53 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E15" s="3">
         <v>29100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>33500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>36400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1564,8 +1587,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1599,216 +1625,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>635900</v>
+      </c>
+      <c r="E17" s="3">
         <v>670000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>605100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>631300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>567600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>593300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>578500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>626800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>568600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>577200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>541200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>569900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>550800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>572800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>556600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>580600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>539900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>605700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>525600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1071400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>517500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>542800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>485600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>857200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>572200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>642500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>580600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>735600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>614800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>115300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>598100</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E18" s="3">
         <v>80600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>64800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>50800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>49300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>59600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>55000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>68400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>90100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>92500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>76400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>88000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>74500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>65200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>91500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>81700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>178400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>95100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>73500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>61600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-91600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>78000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>78700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1348300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>44900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>81400</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1845,52 +1878,53 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-200</v>
       </c>
       <c r="N20" s="3">
         <v>-200</v>
       </c>
       <c r="O20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>300</v>
       </c>
       <c r="R20" s="3">
         <v>300</v>
@@ -1899,257 +1933,263 @@
         <v>300</v>
       </c>
       <c r="T20" s="3">
+        <v>300</v>
+      </c>
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>200</v>
       </c>
       <c r="AA20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH20" s="3">
         <v>1500</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E21" s="3">
         <v>104200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>95400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>83000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>76500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>88500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>51700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>40700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>87200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>103800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>123100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>126200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>113100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>125900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>110500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>100600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>123100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>79300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>112000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>240900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>126700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>105200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>96400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-26500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>109300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>156200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>318700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>77300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="3">
         <v>160300</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E22" s="3">
         <v>10300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>31600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17800</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>3300</v>
       </c>
       <c r="AB22" s="3">
         <v>3300</v>
       </c>
       <c r="AC22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>99400</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>115300</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>3</v>
+      <c r="AH22" s="3">
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>3</v>
@@ -2157,216 +2197,225 @@
       <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E23" s="3">
         <v>57600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>49900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>36500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>35300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-215000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>35800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>68600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>55700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>75700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>63200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>59100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>85900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>37200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>69900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>147400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>77400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>50800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>38400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-109200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-28200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>74600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>78700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>231800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>45000</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH23" s="3">
         <v>82900</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E24" s="3">
         <v>24700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>80200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>35300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-14500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-10300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-40300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-37000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>115300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18800</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2469,216 +2518,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E26" s="3">
         <v>32900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-217400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>51900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>43800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>73500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>44500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>70400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>42500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>80200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>140800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>61800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>91100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>23600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-72200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-17200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>56100</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>62100</v>
       </c>
       <c r="AD26" s="3">
         <v>62100</v>
       </c>
       <c r="AE26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>37900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>154600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>64100</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E27" s="3">
         <v>32900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-217400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>51900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>43800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>73500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>49600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>70400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>42500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>80200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>140800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>61800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>91100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>23600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-72200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-17200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>56100</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>62100</v>
       </c>
       <c r="AD27" s="3">
         <v>62100</v>
       </c>
       <c r="AE27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>37900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>154600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>64100</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2781,8 +2839,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,40 +2887,40 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-2000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>2600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>4500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>43300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>12700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>21000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>9900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>17300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>12000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-38500</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2885,8 +2946,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2989,8 +3053,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3093,52 +3160,55 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>200</v>
       </c>
       <c r="N32" s="3">
         <v>200</v>
       </c>
       <c r="O32" s="3">
+        <v>200</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-300</v>
       </c>
       <c r="R32" s="3">
         <v>-300</v>
@@ -3147,162 +3217,168 @@
         <v>-300</v>
       </c>
       <c r="T32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>-200</v>
       </c>
       <c r="AA32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1017100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E33" s="3">
         <v>32900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-217400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>51900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>43800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>73500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>47600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>47100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>74900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>85800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>92900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>161800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>71700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>108400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-110700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-17200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>56100</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>62100</v>
       </c>
       <c r="AD33" s="3">
         <v>62100</v>
       </c>
       <c r="AE33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>37900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>154600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>64100</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3405,221 +3481,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E35" s="3">
         <v>32900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-217400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>51900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>43800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>73500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>47600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>47100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>74900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>85800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>92900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>161800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>71700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>108400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-110700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-17200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>56100</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>62100</v>
       </c>
       <c r="AD35" s="3">
         <v>62100</v>
       </c>
       <c r="AE35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>37900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>154600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>64100</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45835</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45744</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45562</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45471</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45380</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45198</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44743</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44652</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44470</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44379</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44288</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44106</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44015</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43924</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43644</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43553</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43371</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3656,8 +3741,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3694,92 +3780,93 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1082800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1211700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1133900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1110600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1077300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1069100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>991300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1036200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>948500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>940000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>824200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>651700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>585200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>606900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>568500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>523100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1078300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1073600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>638800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>553900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>441200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>888900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>700800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>822400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>353600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>211200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>193200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,8 +3885,11 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3902,95 +3992,98 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>436600</v>
+      </c>
+      <c r="E43" s="3">
         <v>429600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>405900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>422800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>393100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>363000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>392100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>380600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>413000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>407500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>417100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>415200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>401800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>393500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>392200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>372800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>342600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>331900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>307400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>355000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>358100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>361000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>365400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>306400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>365900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>443600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>456400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3602200</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,95 +4099,98 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300300</v>
+      </c>
+      <c r="E44" s="3">
         <v>288100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>290800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>281900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>261300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>241000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>265600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>263800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>267400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>258800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>278800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>297000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>307200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>300800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>291300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>286000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>280400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>263800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>274300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>311500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>283200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>266900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>257500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>280800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>312300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>277900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>278400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1624300</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4110,8 +4206,11 @@
       <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4133,12 +4232,12 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,54 +4250,54 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>123400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>114000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>206400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>207600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>166500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>545900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>81300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>80800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>73700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>92500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>108100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>82400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>69200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>50500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1328700</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,95 +4313,98 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1919100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2026600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1948300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1934900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1849700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1788300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1797000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1821900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1771900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1743700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1640700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1488900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1414300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1424600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1366000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1388300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1908900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1835800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1766400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1301700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1163300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1590500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1416200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1517700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1114200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1001900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>978500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6009000</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4318,35 +4420,38 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E47" s="3">
         <v>28800</v>
-      </c>
-      <c r="E47" s="3">
-        <v>28700</v>
       </c>
       <c r="F47" s="3">
         <v>28700</v>
       </c>
       <c r="G47" s="3">
+        <v>28700</v>
+      </c>
+      <c r="H47" s="3">
         <v>27100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>26700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4359,8 +4464,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4389,32 +4494,32 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3">
         <v>22300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE47" s="3">
         <v>4938800</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH47" s="3">
-        <v>0</v>
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
@@ -4422,95 +4527,98 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>442300</v>
+      </c>
+      <c r="E48" s="3">
         <v>438900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>436400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>428900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>418400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>419800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>433200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>415800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>431500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>434700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>430600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>429700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>430500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>425400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>409300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>394600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>391200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>392200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>416900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>457800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>451200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>468300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>473900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>483200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>482600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>490400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>484900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17317700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4526,95 +4634,98 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2992800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2985400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3008500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3035700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2953600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2911800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3029900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2981800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4178500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4246200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4459600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4536900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4571900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4583300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4463400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4465700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4097300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4178400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4204600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4574800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4580400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4689900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4642900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4589100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4551100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4591600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4574300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>623900</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4630,8 +4741,11 @@
       <c r="AJ49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4734,8 +4848,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4838,95 +4955,98 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>197400</v>
+      </c>
+      <c r="E52" s="3">
         <v>23600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>220600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>236200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>217600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>250600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>191900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>174400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>180500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>152900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>151700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>158300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>153700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>173200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>212400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>174900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>167800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>174100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>147000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>127000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>127300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>72700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>75200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>70700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>74400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>80700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>626800</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4942,8 +5062,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5046,95 +5169,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5578000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5679000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5642500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5664400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5466400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5350500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5510700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5438100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6556300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6605100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6683800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6607200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6575000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6587000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6411900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6461000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6572300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6574200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6562000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6481300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6321900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6876000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6605700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6665200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6240900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6158300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6118400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>154600</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5150,8 +5276,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5188,8 +5317,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5226,92 +5356,93 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E57" s="3">
         <v>191600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>156000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>171800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>163500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>174600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>172100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>172400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>174700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>179500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>168600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>176800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>186800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>228300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>190000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>182700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>180600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>185800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>171000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>209400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>204600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>235100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>161100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>130900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>194800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>208000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>181400</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5330,92 +5461,95 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E58" s="3">
         <v>39000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>39200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>36100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>151000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>150500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>152000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>150200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>148000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>145600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>144500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>540000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>539200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>510000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>579300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>508600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>507800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>432400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>426700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>421500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>416400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>886800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>253500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>152000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5434,95 +5568,98 @@
       <c r="AJ58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>370900</v>
+      </c>
+      <c r="E59" s="3">
         <v>359100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>384900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>370100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>359300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>317200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>314200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>301200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>286000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>257900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>236700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>250600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>252700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>498400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>489000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>564900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>567300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>590000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>671500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>532300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>515300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>562800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>514000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>445800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>410600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>497300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>427300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5070100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5538,95 +5675,98 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>786600</v>
+      </c>
+      <c r="E60" s="3">
         <v>852600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>821700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>793900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>873300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>878700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>865500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>821400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>781300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>780800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>746800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1150800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1149600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1236700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1258300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1256200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1255700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1208200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1269200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1163200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1136300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1684700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>678900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>830200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>608900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>709200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>760700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17300</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5642,95 +5782,98 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1550500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1558700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1562900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1560100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1409500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1397200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1423000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1492500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1498000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1508000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1493300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>992400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>995100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>870700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>851600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>864100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>876900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>883400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>887800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>893200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>892200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>907700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1755500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1722200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1546700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1321000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1304500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5746,95 +5889,98 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E62" s="3">
         <v>100300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>112500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>114800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>96300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>89800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>103800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>104100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>103700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>103900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>127100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>128100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>126800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>272700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>344100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>324700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>408800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>424600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>457900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>556000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>546100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>562600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>611500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>616900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>599000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>585300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>539200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>329200</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5850,8 +5996,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5954,8 +6103,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6058,8 +6210,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6162,92 +6317,95 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2498500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2572700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2554300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2525400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2430300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2415700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2438200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2461400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2416000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2431200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2390600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2296200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2296000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2380100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2454000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2445000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2541400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2516600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2615300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2612800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2575000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3155400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3048100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3171800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2757200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2618100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2607100</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6266,8 +6424,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6304,8 +6465,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6408,8 +6570,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6512,8 +6677,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6616,8 +6784,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6720,92 +6891,95 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-401700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-440400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-473300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-443000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-469400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-487400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-488600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-496800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>654800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>631200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>848600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>827100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>775200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>731400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>657900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>610300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>563200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>466900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>381100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>288200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>198100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>126400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>75900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>93100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6824,8 +6998,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6928,8 +7105,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7032,8 +7212,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7136,92 +7319,95 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3079500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3106300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3088200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3139000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3036100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2934800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3072500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2976700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4140300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4173900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4293200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4311000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4279000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4206900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3957900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4016000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4030900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4057600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3946700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3868500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3746900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3720600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3557600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3493400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3483700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3540200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3511300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7240,8 +7426,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7344,221 +7533,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45835</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45744</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45562</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45471</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45380</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45198</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44743</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44652</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44470</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44379</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44288</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44106</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44015</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43924</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43644</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43553</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43371</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E81" s="3">
         <v>32900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-217400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>51900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>43800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>73500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>47600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>47100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>74900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>85800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>92900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>161800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>71700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>108400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-110700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-17200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>56100</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>62100</v>
       </c>
       <c r="AD81" s="3">
         <v>62100</v>
       </c>
       <c r="AE81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>37900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>154600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>64100</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7595,112 +7793,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E83" s="3">
         <v>9200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>14200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>35700</v>
       </c>
       <c r="Q83" s="3">
         <v>35700</v>
       </c>
       <c r="R83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="S83" s="3">
         <v>35100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>61900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>33100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>34600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>64900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>77300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>32300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>77400</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7803,8 +8005,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7907,8 +8112,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8011,8 +8219,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8115,8 +8326,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8219,112 +8433,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E89" s="3">
         <v>108000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>78700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>88700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>132400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>70700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>93100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>102000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>95500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>75100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>110300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>46700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>136000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>88300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>137300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>16600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>193400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>148100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-57600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-62300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>187000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>281300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-61800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>210500</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8361,103 +8581,104 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-17500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-28500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>8900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-55200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>0</v>
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
@@ -8465,8 +8686,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8569,8 +8793,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8673,112 +8900,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-69700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-591600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>288600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>15300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>58900</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8815,8 +9048,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8856,8 +9090,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8919,8 +9153,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9023,8 +9260,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9127,8 +9367,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9231,98 +9474,101 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-86400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>114500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-68300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>73700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-463100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-469600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-244400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>733100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>258500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-148100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF100" s="3">
         <v>24300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9335,97 +9581,100 @@
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-46300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-18500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>23100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-9200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>12400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>13600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>10800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>3</v>
@@ -9439,97 +9688,100 @@
       <c r="AJ101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="E102" s="3">
         <v>77800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>23300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>33300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>77800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-44900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>87700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>115800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>172500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>66500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>45400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-555200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>434800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>84900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-335000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-447700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>188100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-121600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>611200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>142400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18000</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
       </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
@@ -9541,6 +9793,9 @@
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
